--- a/data_cripto/btc_cdd.xlsx
+++ b/data_cripto/btc_cdd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5670"/>
+  <dimension ref="A1:B5672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42871,231 +42871,231 @@
     <row r="4245">
       <c r="A4245" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B4245" t="n">
-        <v>3531076.535</v>
+        <v>21669813.785</v>
       </c>
     </row>
     <row r="4246">
       <c r="A4246" t="inlineStr">
         <is>
-          <t>2010-11-02</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="B4246" t="n">
-        <v>242634.954</v>
+        <v>3531076.535</v>
       </c>
     </row>
     <row r="4247">
       <c r="A4247" t="inlineStr">
         <is>
-          <t>2011-01-03</t>
+          <t>2010-11-02</t>
         </is>
       </c>
       <c r="B4247" t="n">
-        <v>254386.201</v>
+        <v>242634.954</v>
       </c>
     </row>
     <row r="4248">
       <c r="A4248" t="inlineStr">
         <is>
-          <t>2011-05-26</t>
+          <t>2011-01-03</t>
         </is>
       </c>
       <c r="B4248" t="n">
-        <v>786506.4350000001</v>
+        <v>254386.201</v>
       </c>
     </row>
     <row r="4249">
       <c r="A4249" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
+          <t>2011-05-26</t>
         </is>
       </c>
       <c r="B4249" t="n">
-        <v>2393980.229</v>
+        <v>786506.4350000001</v>
       </c>
     </row>
     <row r="4250">
       <c r="A4250" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2013-10-13</t>
         </is>
       </c>
       <c r="B4250" t="n">
-        <v>22671673.022</v>
+        <v>2393980.229</v>
       </c>
     </row>
     <row r="4251">
       <c r="A4251" t="inlineStr">
         <is>
-          <t>2013-10-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B4251" t="n">
-        <v>2308581.709</v>
+        <v>22188456.135</v>
       </c>
     </row>
     <row r="4252">
       <c r="A4252" t="inlineStr">
         <is>
-          <t>2013-08-10</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="B4252" t="n">
-        <v>2289095.357</v>
+        <v>22671673.022</v>
       </c>
     </row>
     <row r="4253">
       <c r="A4253" t="inlineStr">
         <is>
-          <t>2012-06-13</t>
+          <t>2013-10-01</t>
         </is>
       </c>
       <c r="B4253" t="n">
-        <v>1377372.783</v>
+        <v>2308581.709</v>
       </c>
     </row>
     <row r="4254">
       <c r="A4254" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2013-08-10</t>
         </is>
       </c>
       <c r="B4254" t="n">
-        <v>18434503.826</v>
+        <v>2289095.357</v>
       </c>
     </row>
     <row r="4255">
       <c r="A4255" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2012-06-13</t>
         </is>
       </c>
       <c r="B4255" t="n">
-        <v>19051529.894</v>
+        <v>1377372.783</v>
       </c>
     </row>
     <row r="4256">
       <c r="A4256" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B4256" t="n">
-        <v>18201052.614</v>
+        <v>18434503.826</v>
       </c>
     </row>
     <row r="4257">
       <c r="A4257" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="B4257" t="n">
-        <v>17984485.196</v>
+        <v>19051529.894</v>
       </c>
     </row>
     <row r="4258">
       <c r="A4258" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B4258" t="n">
-        <v>13705723.752</v>
+        <v>18201052.614</v>
       </c>
     </row>
     <row r="4259">
       <c r="A4259" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B4259" t="n">
-        <v>11581472.882</v>
+        <v>17984485.196</v>
       </c>
     </row>
     <row r="4260">
       <c r="A4260" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B4260" t="n">
-        <v>13291392.364</v>
+        <v>13705723.752</v>
       </c>
     </row>
     <row r="4261">
       <c r="A4261" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B4261" t="n">
-        <v>14621370.416</v>
+        <v>11581472.882</v>
       </c>
     </row>
     <row r="4262">
       <c r="A4262" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="B4262" t="n">
-        <v>7969107.541</v>
+        <v>13291392.364</v>
       </c>
     </row>
     <row r="4263">
       <c r="A4263" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="B4263" t="n">
-        <v>19740098.961</v>
+        <v>14621370.416</v>
       </c>
     </row>
     <row r="4264">
       <c r="A4264" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="B4264" t="n">
-        <v>15350919.159</v>
+        <v>7969107.541</v>
       </c>
     </row>
     <row r="4265">
       <c r="A4265" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B4265" t="n">
-        <v>14823200.021</v>
+        <v>19740098.961</v>
       </c>
     </row>
     <row r="4266">
       <c r="A4266" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="B4266" t="n">
-        <v>21669813.785</v>
+        <v>15350919.159</v>
       </c>
     </row>
     <row r="4267">
       <c r="A4267" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B4267" t="n">
-        <v>22188456.135</v>
+        <v>14823200.021</v>
       </c>
     </row>
     <row r="4268">
@@ -52911,4220 +52911,4240 @@
     <row r="5249">
       <c r="A5249" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B5249" t="n">
-        <v>20506438.825</v>
+        <v>10785396.841</v>
       </c>
     </row>
     <row r="5250">
       <c r="A5250" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B5250" t="n">
-        <v>8310304.394</v>
+        <v>20506438.825</v>
       </c>
     </row>
     <row r="5251">
       <c r="A5251" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="B5251" t="n">
-        <v>9073650.025</v>
+        <v>8310304.394</v>
       </c>
     </row>
     <row r="5252">
       <c r="A5252" t="inlineStr">
         <is>
-          <t>2019-06-04</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="B5252" t="n">
-        <v>7905786.007</v>
+        <v>9073650.025</v>
       </c>
     </row>
     <row r="5253">
       <c r="A5253" t="inlineStr">
         <is>
-          <t>2016-10-09</t>
+          <t>2019-06-04</t>
         </is>
       </c>
       <c r="B5253" t="n">
-        <v>4052991.609</v>
+        <v>7905786.007</v>
       </c>
     </row>
     <row r="5254">
       <c r="A5254" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2016-10-09</t>
         </is>
       </c>
       <c r="B5254" t="n">
-        <v>4466996.197</v>
+        <v>4052991.609</v>
       </c>
     </row>
     <row r="5255">
       <c r="A5255" t="inlineStr">
         <is>
-          <t>2014-11-04</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B5255" t="n">
-        <v>2855446.32</v>
+        <v>4466996.197</v>
       </c>
     </row>
     <row r="5256">
       <c r="A5256" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2014-11-04</t>
         </is>
       </c>
       <c r="B5256" t="n">
-        <v>19218055.445</v>
+        <v>2855446.32</v>
       </c>
     </row>
     <row r="5257">
       <c r="A5257" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B5257" t="n">
-        <v>10164820.626</v>
+        <v>19218055.445</v>
       </c>
     </row>
     <row r="5258">
       <c r="A5258" t="inlineStr">
         <is>
-          <t>2013-12-16</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="B5258" t="n">
-        <v>5816249.876</v>
+        <v>10164820.626</v>
       </c>
     </row>
     <row r="5259">
       <c r="A5259" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2013-12-16</t>
         </is>
       </c>
       <c r="B5259" t="n">
-        <v>14601308.011</v>
+        <v>5816249.876</v>
       </c>
     </row>
     <row r="5260">
       <c r="A5260" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B5260" t="n">
-        <v>12724123.607</v>
+        <v>14601308.011</v>
       </c>
     </row>
     <row r="5261">
       <c r="A5261" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B5261" t="n">
-        <v>14880148.605</v>
+        <v>12724123.607</v>
       </c>
     </row>
     <row r="5262">
       <c r="A5262" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B5262" t="n">
-        <v>9252340.935000001</v>
+        <v>14880148.605</v>
       </c>
     </row>
     <row r="5263">
       <c r="A5263" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="B5263" t="n">
-        <v>9613862.286</v>
+        <v>9252340.935000001</v>
       </c>
     </row>
     <row r="5264">
       <c r="A5264" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="B5264" t="n">
-        <v>12393381.677</v>
+        <v>9613862.286</v>
       </c>
     </row>
     <row r="5265">
       <c r="A5265" t="inlineStr">
         <is>
-          <t>2016-10-23</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="B5265" t="n">
-        <v>4402004.723</v>
+        <v>12393381.677</v>
       </c>
     </row>
     <row r="5266">
       <c r="A5266" t="inlineStr">
         <is>
-          <t>2015-11-07</t>
+          <t>2016-10-23</t>
         </is>
       </c>
       <c r="B5266" t="n">
-        <v>4324186.328</v>
+        <v>4402004.723</v>
       </c>
     </row>
     <row r="5267">
       <c r="A5267" t="inlineStr">
         <is>
-          <t>2010-09-24</t>
+          <t>2015-11-07</t>
         </is>
       </c>
       <c r="B5267" t="n">
-        <v>112259.447</v>
+        <v>4324186.328</v>
       </c>
     </row>
     <row r="5268">
       <c r="A5268" t="inlineStr">
         <is>
-          <t>2014-11-12</t>
+          <t>2010-09-24</t>
         </is>
       </c>
       <c r="B5268" t="n">
-        <v>3023467.834</v>
+        <v>112259.447</v>
       </c>
     </row>
     <row r="5269">
       <c r="A5269" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2014-11-12</t>
         </is>
       </c>
       <c r="B5269" t="n">
-        <v>18218036.776</v>
+        <v>3023467.834</v>
       </c>
     </row>
     <row r="5270">
       <c r="A5270" t="inlineStr">
         <is>
-          <t>2013-12-26</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B5270" t="n">
-        <v>6915819.538</v>
+        <v>18218036.776</v>
       </c>
     </row>
     <row r="5271">
       <c r="A5271" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2013-12-26</t>
         </is>
       </c>
       <c r="B5271" t="n">
-        <v>18095870.058</v>
+        <v>6915819.538</v>
       </c>
     </row>
     <row r="5272">
       <c r="A5272" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B5272" t="n">
-        <v>19014663.42</v>
+        <v>18095870.058</v>
       </c>
     </row>
     <row r="5273">
       <c r="A5273" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="B5273" t="n">
-        <v>9408798.934</v>
+        <v>19014663.42</v>
       </c>
     </row>
     <row r="5274">
       <c r="A5274" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B5274" t="n">
-        <v>16670126.739</v>
+        <v>9408798.934</v>
       </c>
     </row>
     <row r="5275">
       <c r="A5275" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="B5275" t="n">
-        <v>16265749.775</v>
+        <v>16670126.739</v>
       </c>
     </row>
     <row r="5276">
       <c r="A5276" t="inlineStr">
         <is>
-          <t>2021-12-11</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="B5276" t="n">
-        <v>9957806.918</v>
+        <v>16265749.775</v>
       </c>
     </row>
     <row r="5277">
       <c r="A5277" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>2021-12-11</t>
         </is>
       </c>
       <c r="B5277" t="n">
-        <v>11427939.892</v>
+        <v>9957806.918</v>
       </c>
     </row>
     <row r="5278">
       <c r="A5278" t="inlineStr">
         <is>
-          <t>2016-12-09</t>
+          <t>2019-09-19</t>
         </is>
       </c>
       <c r="B5278" t="n">
-        <v>5405479.025</v>
+        <v>11427939.892</v>
       </c>
     </row>
     <row r="5279">
       <c r="A5279" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2016-12-09</t>
         </is>
       </c>
       <c r="B5279" t="n">
-        <v>3557695.791</v>
+        <v>5405479.025</v>
       </c>
     </row>
     <row r="5280">
       <c r="A5280" t="inlineStr">
         <is>
-          <t>2014-11-18</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="B5280" t="n">
-        <v>3039813.332</v>
+        <v>3557695.791</v>
       </c>
     </row>
     <row r="5281">
       <c r="A5281" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2014-11-18</t>
         </is>
       </c>
       <c r="B5281" t="n">
-        <v>21748228.097</v>
+        <v>3039813.332</v>
       </c>
     </row>
     <row r="5282">
       <c r="A5282" t="inlineStr">
         <is>
-          <t>2014-01-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B5282" t="n">
-        <v>6911767.667</v>
+        <v>21748228.097</v>
       </c>
     </row>
     <row r="5283">
       <c r="A5283" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2014-01-10</t>
         </is>
       </c>
       <c r="B5283" t="n">
-        <v>15610517.939</v>
+        <v>6911767.667</v>
       </c>
     </row>
     <row r="5284">
       <c r="A5284" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B5284" t="n">
-        <v>18752011.913</v>
+        <v>15610517.939</v>
       </c>
     </row>
     <row r="5285">
       <c r="A5285" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B5285" t="n">
-        <v>10512254.974</v>
+        <v>18752011.913</v>
       </c>
     </row>
     <row r="5286">
       <c r="A5286" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B5286" t="n">
-        <v>18684510.463</v>
+        <v>10512254.974</v>
       </c>
     </row>
     <row r="5287">
       <c r="A5287" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B5287" t="n">
-        <v>10958641.073</v>
+        <v>18684510.463</v>
       </c>
     </row>
     <row r="5288">
       <c r="A5288" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B5288" t="n">
-        <v>11167233.165</v>
+        <v>10958641.073</v>
       </c>
     </row>
     <row r="5289">
       <c r="A5289" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B5289" t="n">
-        <v>17239012.79</v>
+        <v>11167233.165</v>
       </c>
     </row>
     <row r="5290">
       <c r="A5290" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B5290" t="n">
-        <v>18688241.354</v>
+        <v>17239012.79</v>
       </c>
     </row>
     <row r="5291">
       <c r="A5291" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B5291" t="n">
-        <v>8830961.847999999</v>
+        <v>18688241.354</v>
       </c>
     </row>
     <row r="5292">
       <c r="A5292" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
+          <t>2022-01-28</t>
         </is>
       </c>
       <c r="B5292" t="n">
-        <v>9947791.287</v>
+        <v>8830961.847999999</v>
       </c>
     </row>
     <row r="5293">
       <c r="A5293" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2019-10-07</t>
         </is>
       </c>
       <c r="B5293" t="n">
-        <v>5441150.314</v>
+        <v>9947791.287</v>
       </c>
     </row>
     <row r="5294">
       <c r="A5294" t="inlineStr">
         <is>
-          <t>2015-10-05</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="B5294" t="n">
-        <v>3619797.383</v>
+        <v>5441150.314</v>
       </c>
     </row>
     <row r="5295">
       <c r="A5295" t="inlineStr">
         <is>
-          <t>2014-12-15</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="B5295" t="n">
-        <v>3652983.074</v>
+        <v>3619797.383</v>
       </c>
     </row>
     <row r="5296">
       <c r="A5296" t="inlineStr">
         <is>
-          <t>2014-01-19</t>
+          <t>2014-12-15</t>
         </is>
       </c>
       <c r="B5296" t="n">
-        <v>6709581.37</v>
+        <v>3652983.074</v>
       </c>
     </row>
     <row r="5297">
       <c r="A5297" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2014-01-19</t>
         </is>
       </c>
       <c r="B5297" t="n">
-        <v>22373304.463</v>
+        <v>6709581.37</v>
       </c>
     </row>
     <row r="5298">
       <c r="A5298" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B5298" t="n">
-        <v>14396933.475</v>
+        <v>22373304.463</v>
       </c>
     </row>
     <row r="5299">
       <c r="A5299" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B5299" t="n">
-        <v>14765108.135</v>
+        <v>14396933.475</v>
       </c>
     </row>
     <row r="5300">
       <c r="A5300" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B5300" t="n">
-        <v>12989124.134</v>
+        <v>14765108.135</v>
       </c>
     </row>
     <row r="5301">
       <c r="A5301" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="B5301" t="n">
-        <v>10407093</v>
+        <v>12989124.134</v>
       </c>
     </row>
     <row r="5302">
       <c r="A5302" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B5302" t="n">
-        <v>9996728.27</v>
+        <v>10407093</v>
       </c>
     </row>
     <row r="5303">
       <c r="A5303" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="B5303" t="n">
-        <v>10081112.066</v>
+        <v>9996728.27</v>
       </c>
     </row>
     <row r="5304">
       <c r="A5304" t="inlineStr">
         <is>
-          <t>2016-12-30</t>
+          <t>2019-10-25</t>
         </is>
       </c>
       <c r="B5304" t="n">
-        <v>6503628.164</v>
+        <v>10081112.066</v>
       </c>
     </row>
     <row r="5305">
       <c r="A5305" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
+          <t>2016-12-30</t>
         </is>
       </c>
       <c r="B5305" t="n">
-        <v>3755570.602</v>
+        <v>6503628.164</v>
       </c>
     </row>
     <row r="5306">
       <c r="A5306" t="inlineStr">
         <is>
-          <t>2010-09-21</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="B5306" t="n">
-        <v>111207.989</v>
+        <v>3755570.602</v>
       </c>
     </row>
     <row r="5307">
       <c r="A5307" t="inlineStr">
         <is>
-          <t>2014-12-22</t>
+          <t>2010-09-21</t>
         </is>
       </c>
       <c r="B5307" t="n">
-        <v>3563708.16</v>
+        <v>111207.989</v>
       </c>
     </row>
     <row r="5308">
       <c r="A5308" t="inlineStr">
         <is>
-          <t>2014-01-20</t>
+          <t>2014-12-22</t>
         </is>
       </c>
       <c r="B5308" t="n">
-        <v>6614252.892</v>
+        <v>3563708.16</v>
       </c>
     </row>
     <row r="5309">
       <c r="A5309" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2014-01-20</t>
         </is>
       </c>
       <c r="B5309" t="n">
-        <v>19753403.705</v>
+        <v>6614252.892</v>
       </c>
     </row>
     <row r="5310">
       <c r="A5310" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B5310" t="n">
-        <v>22380338.022</v>
+        <v>19753403.705</v>
       </c>
     </row>
     <row r="5311">
       <c r="A5311" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="B5311" t="n">
-        <v>8685248.65</v>
+        <v>22380338.022</v>
       </c>
     </row>
     <row r="5312">
       <c r="A5312" t="inlineStr">
         <is>
-          <t>2019-12-13</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="B5312" t="n">
-        <v>8145349.405</v>
+        <v>8685248.65</v>
       </c>
     </row>
     <row r="5313">
       <c r="A5313" t="inlineStr">
         <is>
-          <t>2017-01-29</t>
+          <t>2019-12-13</t>
         </is>
       </c>
       <c r="B5313" t="n">
-        <v>7399149.518</v>
+        <v>8145349.405</v>
       </c>
     </row>
     <row r="5314">
       <c r="A5314" t="inlineStr">
         <is>
-          <t>2015-09-03</t>
+          <t>2017-01-29</t>
         </is>
       </c>
       <c r="B5314" t="n">
-        <v>3862063.339</v>
+        <v>7399149.518</v>
       </c>
     </row>
     <row r="5315">
       <c r="A5315" t="inlineStr">
         <is>
-          <t>2011-07-03</t>
+          <t>2015-09-03</t>
         </is>
       </c>
       <c r="B5315" t="n">
-        <v>1736677.834</v>
+        <v>3862063.339</v>
       </c>
     </row>
     <row r="5316">
       <c r="A5316" t="inlineStr">
         <is>
-          <t>2014-12-28</t>
+          <t>2011-07-03</t>
         </is>
       </c>
       <c r="B5316" t="n">
-        <v>3660548.296</v>
+        <v>1736677.834</v>
       </c>
     </row>
     <row r="5317">
       <c r="A5317" t="inlineStr">
         <is>
-          <t>2014-01-23</t>
+          <t>2014-12-28</t>
         </is>
       </c>
       <c r="B5317" t="n">
-        <v>6168423.578</v>
+        <v>3660548.296</v>
       </c>
     </row>
     <row r="5318">
       <c r="A5318" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2014-01-23</t>
         </is>
       </c>
       <c r="B5318" t="n">
-        <v>12847069.898</v>
+        <v>6168423.578</v>
       </c>
     </row>
     <row r="5319">
       <c r="A5319" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B5319" t="n">
-        <v>18949481.536</v>
+        <v>12847069.898</v>
       </c>
     </row>
     <row r="5320">
       <c r="A5320" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2024-12-29</t>
         </is>
       </c>
       <c r="B5320" t="n">
-        <v>21888949.44</v>
+        <v>18949481.536</v>
       </c>
     </row>
     <row r="5321">
       <c r="A5321" t="inlineStr">
         <is>
-          <t>2019-12-29</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B5321" t="n">
-        <v>8042178.284</v>
+        <v>21888949.44</v>
       </c>
     </row>
     <row r="5322">
       <c r="A5322" t="inlineStr">
         <is>
-          <t>2017-04-03</t>
+          <t>2019-12-29</t>
         </is>
       </c>
       <c r="B5322" t="n">
-        <v>9243648.802999999</v>
+        <v>8042178.284</v>
       </c>
     </row>
     <row r="5323">
       <c r="A5323" t="inlineStr">
         <is>
-          <t>2017-02-14</t>
+          <t>2017-04-03</t>
         </is>
       </c>
       <c r="B5323" t="n">
-        <v>7583332.734</v>
+        <v>9243648.802999999</v>
       </c>
     </row>
     <row r="5324">
       <c r="A5324" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
+          <t>2017-02-14</t>
         </is>
       </c>
       <c r="B5324" t="n">
-        <v>992731.454</v>
+        <v>7583332.734</v>
       </c>
     </row>
     <row r="5325">
       <c r="A5325" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="B5325" t="n">
-        <v>3210487.351</v>
+        <v>992731.454</v>
       </c>
     </row>
     <row r="5326">
       <c r="A5326" t="inlineStr">
         <is>
-          <t>2015-01-04</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="B5326" t="n">
-        <v>3639884.552</v>
+        <v>3210487.351</v>
       </c>
     </row>
     <row r="5327">
       <c r="A5327" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2015-01-04</t>
         </is>
       </c>
       <c r="B5327" t="n">
-        <v>20580745.394</v>
+        <v>3639884.552</v>
       </c>
     </row>
     <row r="5328">
       <c r="A5328" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B5328" t="n">
-        <v>9941198.092</v>
+        <v>20580745.394</v>
       </c>
     </row>
     <row r="5329">
       <c r="A5329" t="inlineStr">
         <is>
-          <t>2014-02-10</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="B5329" t="n">
-        <v>6482705.217</v>
+        <v>9941198.092</v>
       </c>
     </row>
     <row r="5330">
       <c r="A5330" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2014-02-10</t>
         </is>
       </c>
       <c r="B5330" t="n">
-        <v>19403702.941</v>
+        <v>6482705.217</v>
       </c>
     </row>
     <row r="5331">
       <c r="A5331" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B5331" t="n">
-        <v>12025387.77</v>
+        <v>19403702.941</v>
       </c>
     </row>
     <row r="5332">
       <c r="A5332" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B5332" t="n">
-        <v>11517746.211</v>
+        <v>12025387.77</v>
       </c>
     </row>
     <row r="5333">
       <c r="A5333" t="inlineStr">
         <is>
-          <t>2020-01-14</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B5333" t="n">
-        <v>7135383.216</v>
+        <v>11517746.211</v>
       </c>
     </row>
     <row r="5334">
       <c r="A5334" t="inlineStr">
         <is>
-          <t>2017-02-15</t>
+          <t>2020-01-14</t>
         </is>
       </c>
       <c r="B5334" t="n">
-        <v>7448825.404</v>
+        <v>7135383.216</v>
       </c>
     </row>
     <row r="5335">
       <c r="A5335" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-02-15</t>
         </is>
       </c>
       <c r="B5335" t="n">
-        <v>2814354.291</v>
+        <v>7448825.404</v>
       </c>
     </row>
     <row r="5336">
       <c r="A5336" t="inlineStr">
         <is>
-          <t>2015-01-18</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="B5336" t="n">
-        <v>4062626.204</v>
+        <v>2814354.291</v>
       </c>
     </row>
     <row r="5337">
       <c r="A5337" t="inlineStr">
         <is>
-          <t>2011-09-27</t>
+          <t>2015-01-18</t>
         </is>
       </c>
       <c r="B5337" t="n">
-        <v>744327.885</v>
+        <v>4062626.204</v>
       </c>
     </row>
     <row r="5338">
       <c r="A5338" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
+          <t>2011-09-27</t>
         </is>
       </c>
       <c r="B5338" t="n">
-        <v>10037167.8</v>
+        <v>744327.885</v>
       </c>
     </row>
     <row r="5339">
       <c r="A5339" t="inlineStr">
         <is>
-          <t>2014-02-14</t>
+          <t>2022-04-19</t>
         </is>
       </c>
       <c r="B5339" t="n">
-        <v>6165888.39</v>
+        <v>10037167.8</v>
       </c>
     </row>
     <row r="5340">
       <c r="A5340" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2014-02-14</t>
         </is>
       </c>
       <c r="B5340" t="n">
-        <v>18648006.799</v>
+        <v>6165888.39</v>
       </c>
     </row>
     <row r="5341">
       <c r="A5341" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B5341" t="n">
-        <v>18754649.599</v>
+        <v>18648006.799</v>
       </c>
     </row>
     <row r="5342">
       <c r="A5342" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B5342" t="n">
-        <v>18605805.647</v>
+        <v>18754649.599</v>
       </c>
     </row>
     <row r="5343">
       <c r="A5343" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B5343" t="n">
-        <v>22464882.776</v>
+        <v>18605805.647</v>
       </c>
     </row>
     <row r="5344">
       <c r="A5344" t="inlineStr">
         <is>
-          <t>2020-03-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B5344" t="n">
-        <v>8319527.642</v>
+        <v>22464882.776</v>
       </c>
     </row>
     <row r="5345">
       <c r="A5345" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2020-03-18</t>
         </is>
       </c>
       <c r="B5345" t="n">
-        <v>19382954.778</v>
+        <v>8319527.642</v>
       </c>
     </row>
     <row r="5346">
       <c r="A5346" t="inlineStr">
         <is>
-          <t>2017-03-06</t>
+          <t>2017-08-24</t>
         </is>
       </c>
       <c r="B5346" t="n">
-        <v>7818647.054</v>
+        <v>19382954.778</v>
       </c>
     </row>
     <row r="5347">
       <c r="A5347" t="inlineStr">
         <is>
-          <t>2015-07-05</t>
+          <t>2017-03-06</t>
         </is>
       </c>
       <c r="B5347" t="n">
-        <v>2590237.539</v>
+        <v>7818647.054</v>
       </c>
     </row>
     <row r="5348">
       <c r="A5348" t="inlineStr">
         <is>
-          <t>2015-01-26</t>
+          <t>2015-07-05</t>
         </is>
       </c>
       <c r="B5348" t="n">
-        <v>4227141.883</v>
+        <v>2590237.539</v>
       </c>
     </row>
     <row r="5349">
       <c r="A5349" t="inlineStr">
         <is>
-          <t>2011-10-11</t>
+          <t>2015-01-26</t>
         </is>
       </c>
       <c r="B5349" t="n">
-        <v>733876.334</v>
+        <v>4227141.883</v>
       </c>
     </row>
     <row r="5350">
       <c r="A5350" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2011-10-11</t>
         </is>
       </c>
       <c r="B5350" t="n">
-        <v>10152904.599</v>
+        <v>733876.334</v>
       </c>
     </row>
     <row r="5351">
       <c r="A5351" t="inlineStr">
         <is>
-          <t>2014-02-26</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="B5351" t="n">
-        <v>4892785.663</v>
+        <v>10152904.599</v>
       </c>
     </row>
     <row r="5352">
       <c r="A5352" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2014-02-26</t>
         </is>
       </c>
       <c r="B5352" t="n">
-        <v>19098735.371</v>
+        <v>4892785.663</v>
       </c>
     </row>
     <row r="5353">
       <c r="A5353" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B5353" t="n">
-        <v>11437944.275</v>
+        <v>19098735.371</v>
       </c>
     </row>
     <row r="5354">
       <c r="A5354" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B5354" t="n">
-        <v>15630701.474</v>
+        <v>11437944.275</v>
       </c>
     </row>
     <row r="5355">
       <c r="A5355" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B5355" t="n">
-        <v>11711443.8</v>
+        <v>15630701.474</v>
       </c>
     </row>
     <row r="5356">
       <c r="A5356" t="inlineStr">
         <is>
-          <t>2020-04-04</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B5356" t="n">
-        <v>8278468.575</v>
+        <v>11711443.8</v>
       </c>
     </row>
     <row r="5357">
       <c r="A5357" t="inlineStr">
         <is>
-          <t>2017-03-12</t>
+          <t>2020-04-04</t>
         </is>
       </c>
       <c r="B5357" t="n">
-        <v>8015167.541</v>
+        <v>8278468.575</v>
       </c>
     </row>
     <row r="5358">
       <c r="A5358" t="inlineStr">
         <is>
-          <t>2015-06-08</t>
+          <t>2017-03-12</t>
         </is>
       </c>
       <c r="B5358" t="n">
-        <v>2384540.357</v>
+        <v>8015167.541</v>
       </c>
     </row>
     <row r="5359">
       <c r="A5359" t="inlineStr">
         <is>
-          <t>2015-02-02</t>
+          <t>2015-06-08</t>
         </is>
       </c>
       <c r="B5359" t="n">
-        <v>4214903.008</v>
+        <v>2384540.357</v>
       </c>
     </row>
     <row r="5360">
       <c r="A5360" t="inlineStr">
         <is>
-          <t>2011-10-28</t>
+          <t>2015-02-02</t>
         </is>
       </c>
       <c r="B5360" t="n">
-        <v>735721.417</v>
+        <v>4214903.008</v>
       </c>
     </row>
     <row r="5361">
       <c r="A5361" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2011-10-28</t>
         </is>
       </c>
       <c r="B5361" t="n">
-        <v>8620307.16</v>
+        <v>735721.417</v>
       </c>
     </row>
     <row r="5362">
       <c r="A5362" t="inlineStr">
         <is>
-          <t>2014-03-15</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="B5362" t="n">
-        <v>6519122.467</v>
+        <v>8620307.16</v>
       </c>
     </row>
     <row r="5363">
       <c r="A5363" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2014-03-15</t>
         </is>
       </c>
       <c r="B5363" t="n">
-        <v>18515818.574</v>
+        <v>6519122.467</v>
       </c>
     </row>
     <row r="5364">
       <c r="A5364" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B5364" t="n">
-        <v>12856671.682</v>
+        <v>18515818.574</v>
       </c>
     </row>
     <row r="5365">
       <c r="A5365" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B5365" t="n">
-        <v>18201448.889</v>
+        <v>12856671.682</v>
       </c>
     </row>
     <row r="5366">
       <c r="A5366" t="inlineStr">
         <is>
-          <t>2020-04-25</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B5366" t="n">
-        <v>7919062.632</v>
+        <v>18201448.889</v>
       </c>
     </row>
     <row r="5367">
       <c r="A5367" t="inlineStr">
         <is>
-          <t>2017-03-21</t>
+          <t>2020-04-25</t>
         </is>
       </c>
       <c r="B5367" t="n">
-        <v>8412562.749</v>
+        <v>7919062.632</v>
       </c>
     </row>
     <row r="5368">
       <c r="A5368" t="inlineStr">
         <is>
-          <t>2015-05-09</t>
+          <t>2017-03-21</t>
         </is>
       </c>
       <c r="B5368" t="n">
-        <v>3219850.774</v>
+        <v>8412562.749</v>
       </c>
     </row>
     <row r="5369">
       <c r="A5369" t="inlineStr">
         <is>
-          <t>2015-02-09</t>
+          <t>2015-05-09</t>
         </is>
       </c>
       <c r="B5369" t="n">
-        <v>4096290.662</v>
+        <v>3219850.774</v>
       </c>
     </row>
     <row r="5370">
       <c r="A5370" t="inlineStr">
         <is>
-          <t>2011-10-31</t>
+          <t>2015-02-09</t>
         </is>
       </c>
       <c r="B5370" t="n">
-        <v>732160.326</v>
+        <v>4096290.662</v>
       </c>
     </row>
     <row r="5371">
       <c r="A5371" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2011-10-31</t>
         </is>
       </c>
       <c r="B5371" t="n">
-        <v>9519524.592</v>
+        <v>732160.326</v>
       </c>
     </row>
     <row r="5372">
       <c r="A5372" t="inlineStr">
         <is>
-          <t>2014-03-18</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="B5372" t="n">
-        <v>6370558.748</v>
+        <v>9519524.592</v>
       </c>
     </row>
     <row r="5373">
       <c r="A5373" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2014-03-18</t>
         </is>
       </c>
       <c r="B5373" t="n">
-        <v>18421861.334</v>
+        <v>6370558.748</v>
       </c>
     </row>
     <row r="5374">
       <c r="A5374" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B5374" t="n">
-        <v>18398573.918</v>
+        <v>18421861.334</v>
       </c>
     </row>
     <row r="5375">
       <c r="A5375" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B5375" t="n">
-        <v>7287456.154</v>
+        <v>18398573.918</v>
       </c>
     </row>
     <row r="5376">
       <c r="A5376" t="inlineStr">
         <is>
-          <t>2017-04-09</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="B5376" t="n">
-        <v>8810606.551000001</v>
+        <v>7287456.154</v>
       </c>
     </row>
     <row r="5377">
       <c r="A5377" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
+          <t>2017-04-09</t>
         </is>
       </c>
       <c r="B5377" t="n">
-        <v>3585584.01</v>
+        <v>8810606.551000001</v>
       </c>
     </row>
     <row r="5378">
       <c r="A5378" t="inlineStr">
         <is>
-          <t>2015-03-02</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="B5378" t="n">
-        <v>3933274.224</v>
+        <v>3585584.01</v>
       </c>
     </row>
     <row r="5379">
       <c r="A5379" t="inlineStr">
         <is>
-          <t>2011-11-14</t>
+          <t>2015-03-02</t>
         </is>
       </c>
       <c r="B5379" t="n">
-        <v>826121.591</v>
+        <v>3933274.224</v>
       </c>
     </row>
     <row r="5380">
       <c r="A5380" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2011-11-14</t>
         </is>
       </c>
       <c r="B5380" t="n">
-        <v>9308642.501</v>
+        <v>826121.591</v>
       </c>
     </row>
     <row r="5381">
       <c r="A5381" t="inlineStr">
         <is>
-          <t>2014-04-06</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="B5381" t="n">
-        <v>5505621.837</v>
+        <v>9308642.501</v>
       </c>
     </row>
     <row r="5382">
       <c r="A5382" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2014-04-06</t>
         </is>
       </c>
       <c r="B5382" t="n">
-        <v>17331183.271</v>
+        <v>5505621.837</v>
       </c>
     </row>
     <row r="5383">
       <c r="A5383" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B5383" t="n">
-        <v>10333719.079</v>
+        <v>17331183.271</v>
       </c>
     </row>
     <row r="5384">
       <c r="A5384" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B5384" t="n">
-        <v>20059958.476</v>
+        <v>10333719.079</v>
       </c>
     </row>
     <row r="5385">
       <c r="A5385" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B5385" t="n">
-        <v>6907432.252</v>
+        <v>20059958.476</v>
       </c>
     </row>
     <row r="5386">
       <c r="A5386" t="inlineStr">
         <is>
-          <t>2017-04-20</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="B5386" t="n">
-        <v>8967425.550000001</v>
+        <v>6907432.252</v>
       </c>
     </row>
     <row r="5387">
       <c r="A5387" t="inlineStr">
         <is>
-          <t>2015-03-09</t>
+          <t>2017-04-20</t>
         </is>
       </c>
       <c r="B5387" t="n">
-        <v>3900348.066</v>
+        <v>8967425.550000001</v>
       </c>
     </row>
     <row r="5388">
       <c r="A5388" t="inlineStr">
         <is>
-          <t>2011-11-16</t>
+          <t>2015-03-09</t>
         </is>
       </c>
       <c r="B5388" t="n">
-        <v>1048736.803</v>
+        <v>3900348.066</v>
       </c>
     </row>
     <row r="5389">
       <c r="A5389" t="inlineStr">
         <is>
-          <t>2015-03-08</t>
+          <t>2011-11-16</t>
         </is>
       </c>
       <c r="B5389" t="n">
-        <v>3986897.712</v>
+        <v>1048736.803</v>
       </c>
     </row>
     <row r="5390">
       <c r="A5390" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2015-03-08</t>
         </is>
       </c>
       <c r="B5390" t="n">
-        <v>9481051.257999999</v>
+        <v>3986897.712</v>
       </c>
     </row>
     <row r="5391">
       <c r="A5391" t="inlineStr">
         <is>
-          <t>2014-04-27</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="B5391" t="n">
-        <v>5438426.506</v>
+        <v>9481051.257999999</v>
       </c>
     </row>
     <row r="5392">
       <c r="A5392" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2014-04-27</t>
         </is>
       </c>
       <c r="B5392" t="n">
-        <v>12972917.766</v>
+        <v>5438426.506</v>
       </c>
     </row>
     <row r="5393">
       <c r="A5393" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="B5393" t="n">
-        <v>12827728.942</v>
+        <v>12972917.766</v>
       </c>
     </row>
     <row r="5394">
       <c r="A5394" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B5394" t="n">
-        <v>10843259.392</v>
+        <v>12827728.942</v>
       </c>
     </row>
     <row r="5395">
       <c r="A5395" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B5395" t="n">
-        <v>16829264.336</v>
+        <v>10843259.392</v>
       </c>
     </row>
     <row r="5396">
       <c r="A5396" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="B5396" t="n">
-        <v>19069569.049</v>
+        <v>16829264.336</v>
       </c>
     </row>
     <row r="5397">
       <c r="A5397" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B5397" t="n">
-        <v>6721984.554</v>
+        <v>19069569.049</v>
       </c>
     </row>
     <row r="5398">
       <c r="A5398" t="inlineStr">
         <is>
-          <t>2017-04-30</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="B5398" t="n">
-        <v>8922467.217</v>
+        <v>6721984.554</v>
       </c>
     </row>
     <row r="5399">
       <c r="A5399" t="inlineStr">
         <is>
-          <t>2015-03-22</t>
+          <t>2017-04-30</t>
         </is>
       </c>
       <c r="B5399" t="n">
-        <v>4135797.457</v>
+        <v>8922467.217</v>
       </c>
     </row>
     <row r="5400">
       <c r="A5400" t="inlineStr">
         <is>
-          <t>2015-03-06</t>
+          <t>2015-03-22</t>
         </is>
       </c>
       <c r="B5400" t="n">
-        <v>4074719.188</v>
+        <v>4135797.457</v>
       </c>
     </row>
     <row r="5401">
       <c r="A5401" t="inlineStr">
         <is>
-          <t>2011-11-19</t>
+          <t>2015-03-06</t>
         </is>
       </c>
       <c r="B5401" t="n">
-        <v>1086764.653</v>
+        <v>4074719.188</v>
       </c>
     </row>
     <row r="5402">
       <c r="A5402" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2011-11-19</t>
         </is>
       </c>
       <c r="B5402" t="n">
-        <v>9532015.716</v>
+        <v>1086764.653</v>
       </c>
     </row>
     <row r="5403">
       <c r="A5403" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
+          <t>2022-08-06</t>
         </is>
       </c>
       <c r="B5403" t="n">
-        <v>4343530.167</v>
+        <v>9532015.716</v>
       </c>
     </row>
     <row r="5404">
       <c r="A5404" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="B5404" t="n">
-        <v>17480511.655</v>
+        <v>4343530.167</v>
       </c>
     </row>
     <row r="5405">
       <c r="A5405" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B5405" t="n">
-        <v>12893419.954</v>
+        <v>17480511.655</v>
       </c>
     </row>
     <row r="5406">
       <c r="A5406" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B5406" t="n">
-        <v>18930025.11</v>
+        <v>12893419.954</v>
       </c>
     </row>
     <row r="5407">
       <c r="A5407" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="B5407" t="n">
-        <v>13592327.934</v>
+        <v>18930025.11</v>
       </c>
     </row>
     <row r="5408">
       <c r="A5408" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B5408" t="n">
-        <v>16884075.838</v>
+        <v>13592327.934</v>
       </c>
     </row>
     <row r="5409">
       <c r="A5409" t="inlineStr">
         <is>
-          <t>2020-07-05</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="B5409" t="n">
-        <v>5802826.225</v>
+        <v>16884075.838</v>
       </c>
     </row>
     <row r="5410">
       <c r="A5410" t="inlineStr">
         <is>
-          <t>2019-02-17</t>
+          <t>2020-07-05</t>
         </is>
       </c>
       <c r="B5410" t="n">
-        <v>15295963.935</v>
+        <v>5802826.225</v>
       </c>
     </row>
     <row r="5411">
       <c r="A5411" t="inlineStr">
         <is>
-          <t>2017-05-17</t>
+          <t>2019-02-17</t>
         </is>
       </c>
       <c r="B5411" t="n">
-        <v>10300409.588</v>
+        <v>15295963.935</v>
       </c>
     </row>
     <row r="5412">
       <c r="A5412" t="inlineStr">
         <is>
-          <t>2015-03-29</t>
+          <t>2017-05-17</t>
         </is>
       </c>
       <c r="B5412" t="n">
-        <v>3988633.591</v>
+        <v>10300409.588</v>
       </c>
     </row>
     <row r="5413">
       <c r="A5413" t="inlineStr">
         <is>
-          <t>2015-02-14</t>
+          <t>2015-03-29</t>
         </is>
       </c>
       <c r="B5413" t="n">
-        <v>4056897.67</v>
+        <v>3988633.591</v>
       </c>
     </row>
     <row r="5414">
       <c r="A5414" t="inlineStr">
         <is>
-          <t>2011-12-03</t>
+          <t>2015-02-14</t>
         </is>
       </c>
       <c r="B5414" t="n">
-        <v>1095387.925</v>
+        <v>4056897.67</v>
       </c>
     </row>
     <row r="5415">
       <c r="A5415" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2011-12-03</t>
         </is>
       </c>
       <c r="B5415" t="n">
-        <v>8363509.02</v>
+        <v>1095387.925</v>
       </c>
     </row>
     <row r="5416">
       <c r="A5416" t="inlineStr">
         <is>
-          <t>2014-06-28</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="B5416" t="n">
-        <v>2686947.84</v>
+        <v>8363509.02</v>
       </c>
     </row>
     <row r="5417">
       <c r="A5417" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2014-06-28</t>
         </is>
       </c>
       <c r="B5417" t="n">
-        <v>12458643.374</v>
+        <v>2686947.84</v>
       </c>
     </row>
     <row r="5418">
       <c r="A5418" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B5418" t="n">
-        <v>11641354.93</v>
+        <v>12458643.374</v>
       </c>
     </row>
     <row r="5419">
       <c r="A5419" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B5419" t="n">
-        <v>16833334.95</v>
+        <v>11641354.93</v>
       </c>
     </row>
     <row r="5420">
       <c r="A5420" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B5420" t="n">
-        <v>17359924.278</v>
+        <v>16833334.95</v>
       </c>
     </row>
     <row r="5421">
       <c r="A5421" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="B5421" t="n">
-        <v>10236215.389</v>
+        <v>17359924.278</v>
       </c>
     </row>
     <row r="5422">
       <c r="A5422" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="B5422" t="n">
-        <v>6065155.983</v>
+        <v>10236215.389</v>
       </c>
     </row>
     <row r="5423">
       <c r="A5423" t="inlineStr">
         <is>
-          <t>2017-06-01</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B5423" t="n">
-        <v>11531744.112</v>
+        <v>6065155.983</v>
       </c>
     </row>
     <row r="5424">
       <c r="A5424" t="inlineStr">
         <is>
-          <t>2015-04-06</t>
+          <t>2017-06-01</t>
         </is>
       </c>
       <c r="B5424" t="n">
-        <v>3694404.674</v>
+        <v>11531744.112</v>
       </c>
     </row>
     <row r="5425">
       <c r="A5425" t="inlineStr">
         <is>
-          <t>2015-01-31</t>
+          <t>2015-04-06</t>
         </is>
       </c>
       <c r="B5425" t="n">
-        <v>4218195.556</v>
+        <v>3694404.674</v>
       </c>
     </row>
     <row r="5426">
       <c r="A5426" t="inlineStr">
         <is>
-          <t>2011-12-17</t>
+          <t>2015-01-31</t>
         </is>
       </c>
       <c r="B5426" t="n">
-        <v>1066127.172</v>
+        <v>4218195.556</v>
       </c>
     </row>
     <row r="5427">
       <c r="A5427" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
+          <t>2011-12-17</t>
         </is>
       </c>
       <c r="B5427" t="n">
-        <v>8049967.714</v>
+        <v>1066127.172</v>
       </c>
     </row>
     <row r="5428">
       <c r="A5428" t="inlineStr">
         <is>
-          <t>2014-07-16</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="B5428" t="n">
-        <v>2436383.016</v>
+        <v>8049967.714</v>
       </c>
     </row>
     <row r="5429">
       <c r="A5429" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2014-07-16</t>
         </is>
       </c>
       <c r="B5429" t="n">
-        <v>18172193.247</v>
+        <v>2436383.016</v>
       </c>
     </row>
     <row r="5430">
       <c r="A5430" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B5430" t="n">
-        <v>18249350.163</v>
+        <v>18172193.247</v>
       </c>
     </row>
     <row r="5431">
       <c r="A5431" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B5431" t="n">
-        <v>19357870.444</v>
+        <v>18249350.163</v>
       </c>
     </row>
     <row r="5432">
       <c r="A5432" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B5432" t="n">
-        <v>18829096.598</v>
+        <v>19357870.444</v>
       </c>
     </row>
     <row r="5433">
       <c r="A5433" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B5433" t="n">
-        <v>11410435.924</v>
+        <v>18829096.598</v>
       </c>
     </row>
     <row r="5434">
       <c r="A5434" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="B5434" t="n">
-        <v>11511228.874</v>
+        <v>11410435.924</v>
       </c>
     </row>
     <row r="5435">
       <c r="A5435" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="B5435" t="n">
-        <v>11873870.808</v>
+        <v>11511228.874</v>
       </c>
     </row>
     <row r="5436">
       <c r="A5436" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="B5436" t="n">
-        <v>16905626.816</v>
+        <v>11873870.808</v>
       </c>
     </row>
     <row r="5437">
       <c r="A5437" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B5437" t="n">
-        <v>9506750.107999999</v>
+        <v>16905626.816</v>
       </c>
     </row>
     <row r="5438">
       <c r="A5438" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="B5438" t="n">
-        <v>10121188.898</v>
+        <v>9506750.107999999</v>
       </c>
     </row>
     <row r="5439">
       <c r="A5439" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="B5439" t="n">
-        <v>15731904.375</v>
+        <v>10121188.898</v>
       </c>
     </row>
     <row r="5440">
       <c r="A5440" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="B5440" t="n">
-        <v>6820551.817</v>
+        <v>15731904.375</v>
       </c>
     </row>
     <row r="5441">
       <c r="A5441" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B5441" t="n">
-        <v>11905850.214</v>
+        <v>6820551.817</v>
       </c>
     </row>
     <row r="5442">
       <c r="A5442" t="inlineStr">
         <is>
-          <t>2015-04-12</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="B5442" t="n">
-        <v>3600337.897</v>
+        <v>11905850.214</v>
       </c>
     </row>
     <row r="5443">
       <c r="A5443" t="inlineStr">
         <is>
-          <t>2015-01-23</t>
+          <t>2015-04-12</t>
         </is>
       </c>
       <c r="B5443" t="n">
-        <v>4111883.874</v>
+        <v>3600337.897</v>
       </c>
     </row>
     <row r="5444">
       <c r="A5444" t="inlineStr">
         <is>
-          <t>2012-01-03</t>
+          <t>2015-01-23</t>
         </is>
       </c>
       <c r="B5444" t="n">
-        <v>1178238.791</v>
+        <v>4111883.874</v>
       </c>
     </row>
     <row r="5445">
       <c r="A5445" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2012-01-03</t>
         </is>
       </c>
       <c r="B5445" t="n">
-        <v>6358468.879</v>
+        <v>1178238.791</v>
       </c>
     </row>
     <row r="5446">
       <c r="A5446" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="B5446" t="n">
-        <v>2826869.713</v>
+        <v>6358468.879</v>
       </c>
     </row>
     <row r="5447">
       <c r="A5447" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="B5447" t="n">
-        <v>16560800.359</v>
+        <v>2826869.713</v>
       </c>
     </row>
     <row r="5448">
       <c r="A5448" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B5448" t="n">
-        <v>18211536.318</v>
+        <v>16560800.359</v>
       </c>
     </row>
     <row r="5449">
       <c r="A5449" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B5449" t="n">
-        <v>11004721.176</v>
+        <v>18211536.318</v>
       </c>
     </row>
     <row r="5450">
       <c r="A5450" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B5450" t="n">
-        <v>11867652.532</v>
+        <v>11004721.176</v>
       </c>
     </row>
     <row r="5451">
       <c r="A5451" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="B5451" t="n">
-        <v>12210206.289</v>
+        <v>11867652.532</v>
       </c>
     </row>
     <row r="5452">
       <c r="A5452" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B5452" t="n">
-        <v>14873483.781</v>
+        <v>12210206.289</v>
       </c>
     </row>
     <row r="5453">
       <c r="A5453" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B5453" t="n">
-        <v>6837460.05</v>
+        <v>14873483.781</v>
       </c>
     </row>
     <row r="5454">
       <c r="A5454" t="inlineStr">
         <is>
-          <t>2017-08-15</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B5454" t="n">
-        <v>19566598.77</v>
+        <v>6837460.05</v>
       </c>
     </row>
     <row r="5455">
       <c r="A5455" t="inlineStr">
         <is>
-          <t>2015-04-19</t>
+          <t>2017-08-15</t>
         </is>
       </c>
       <c r="B5455" t="n">
-        <v>3445407.103</v>
+        <v>19566598.77</v>
       </c>
     </row>
     <row r="5456">
       <c r="A5456" t="inlineStr">
         <is>
-          <t>2015-01-12</t>
+          <t>2015-04-19</t>
         </is>
       </c>
       <c r="B5456" t="n">
-        <v>3848368.662</v>
+        <v>3445407.103</v>
       </c>
     </row>
     <row r="5457">
       <c r="A5457" t="inlineStr">
         <is>
-          <t>2012-01-20</t>
+          <t>2015-01-12</t>
         </is>
       </c>
       <c r="B5457" t="n">
-        <v>1244736.785</v>
+        <v>3848368.662</v>
       </c>
     </row>
     <row r="5458">
       <c r="A5458" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2012-01-20</t>
         </is>
       </c>
       <c r="B5458" t="n">
-        <v>8536718.226</v>
+        <v>1244736.785</v>
       </c>
     </row>
     <row r="5459">
       <c r="A5459" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="B5459" t="n">
-        <v>2925697.333</v>
+        <v>8536718.226</v>
       </c>
     </row>
     <row r="5460">
       <c r="A5460" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="B5460" t="n">
-        <v>12171617.905</v>
+        <v>2925697.333</v>
       </c>
     </row>
     <row r="5461">
       <c r="A5461" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B5461" t="n">
-        <v>13510242.654</v>
+        <v>12171617.905</v>
       </c>
     </row>
     <row r="5462">
       <c r="A5462" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B5462" t="n">
-        <v>19772264.652</v>
+        <v>13510242.654</v>
       </c>
     </row>
     <row r="5463">
       <c r="A5463" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="B5463" t="n">
-        <v>16050259.512</v>
+        <v>19772264.652</v>
       </c>
     </row>
     <row r="5464">
       <c r="A5464" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B5464" t="n">
-        <v>11104807.404</v>
+        <v>16050259.512</v>
       </c>
     </row>
     <row r="5465">
       <c r="A5465" t="inlineStr">
         <is>
-          <t>2017-08-28</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B5465" t="n">
-        <v>19422838.72</v>
+        <v>11104807.404</v>
       </c>
     </row>
     <row r="5466">
       <c r="A5466" t="inlineStr">
         <is>
-          <t>2015-04-25</t>
+          <t>2017-08-28</t>
         </is>
       </c>
       <c r="B5466" t="n">
-        <v>3352942.164</v>
+        <v>19422838.72</v>
       </c>
     </row>
     <row r="5467">
       <c r="A5467" t="inlineStr">
         <is>
-          <t>2014-12-25</t>
+          <t>2015-04-25</t>
         </is>
       </c>
       <c r="B5467" t="n">
-        <v>3724068.626</v>
+        <v>3352942.164</v>
       </c>
     </row>
     <row r="5468">
       <c r="A5468" t="inlineStr">
         <is>
-          <t>2012-01-21</t>
+          <t>2014-12-25</t>
         </is>
       </c>
       <c r="B5468" t="n">
-        <v>1246443.905</v>
+        <v>3724068.626</v>
       </c>
     </row>
     <row r="5469">
       <c r="A5469" t="inlineStr">
         <is>
-          <t>2022-11-23</t>
+          <t>2012-01-21</t>
         </is>
       </c>
       <c r="B5469" t="n">
-        <v>10451472.456</v>
+        <v>1246443.905</v>
       </c>
     </row>
     <row r="5470">
       <c r="A5470" t="inlineStr">
         <is>
-          <t>2014-09-13</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="B5470" t="n">
-        <v>2524791.779</v>
+        <v>10451472.456</v>
       </c>
     </row>
     <row r="5471">
       <c r="A5471" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2014-09-13</t>
         </is>
       </c>
       <c r="B5471" t="n">
-        <v>14362928.781</v>
+        <v>2524791.779</v>
       </c>
     </row>
     <row r="5472">
       <c r="A5472" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5472" t="n">
-        <v>13491078.904</v>
+        <v>14362928.781</v>
       </c>
     </row>
     <row r="5473">
       <c r="A5473" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B5473" t="n">
-        <v>20112719.639</v>
+        <v>13491078.904</v>
       </c>
     </row>
     <row r="5474">
       <c r="A5474" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B5474" t="n">
-        <v>20351324.136</v>
+        <v>20112719.639</v>
       </c>
     </row>
     <row r="5475">
       <c r="A5475" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B5475" t="n">
-        <v>13156711.485</v>
+        <v>20351324.136</v>
       </c>
     </row>
     <row r="5476">
       <c r="A5476" t="inlineStr">
         <is>
-          <t>2017-09-08</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B5476" t="n">
-        <v>19486335.788</v>
+        <v>13156711.485</v>
       </c>
     </row>
     <row r="5477">
       <c r="A5477" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2017-09-08</t>
         </is>
       </c>
       <c r="B5477" t="n">
-        <v>3177021.142</v>
+        <v>19486335.788</v>
       </c>
     </row>
     <row r="5478">
       <c r="A5478" t="inlineStr">
         <is>
-          <t>2014-12-02</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="B5478" t="n">
-        <v>3340414.9</v>
+        <v>3177021.142</v>
       </c>
     </row>
     <row r="5479">
       <c r="A5479" t="inlineStr">
         <is>
-          <t>2014-10-02</t>
+          <t>2014-12-02</t>
         </is>
       </c>
       <c r="B5479" t="n">
-        <v>2628371.334</v>
+        <v>3340414.9</v>
       </c>
     </row>
     <row r="5480">
       <c r="A5480" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="B5480" t="n">
-        <v>23088144.912</v>
+        <v>2628371.334</v>
       </c>
     </row>
     <row r="5481">
       <c r="A5481" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B5481" t="n">
-        <v>14103054.216</v>
+        <v>23088144.912</v>
       </c>
     </row>
     <row r="5482">
       <c r="A5482" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B5482" t="n">
-        <v>19939698.057</v>
+        <v>14103054.216</v>
       </c>
     </row>
     <row r="5483">
       <c r="A5483" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="B5483" t="n">
-        <v>18996084.867</v>
+        <v>19939698.057</v>
       </c>
     </row>
     <row r="5484">
       <c r="A5484" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B5484" t="n">
-        <v>10152643.862</v>
+        <v>18996084.867</v>
       </c>
     </row>
     <row r="5485">
       <c r="A5485" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="B5485" t="n">
-        <v>10510937.957</v>
+        <v>10152643.862</v>
       </c>
     </row>
     <row r="5486">
       <c r="A5486" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="B5486" t="n">
-        <v>15716836.044</v>
+        <v>10510937.957</v>
       </c>
     </row>
     <row r="5487">
       <c r="A5487" t="inlineStr">
         <is>
-          <t>2012-01-26</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="B5487" t="n">
-        <v>1264128.557</v>
+        <v>15716836.044</v>
       </c>
     </row>
     <row r="5488">
       <c r="A5488" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2012-01-26</t>
         </is>
       </c>
       <c r="B5488" t="n">
-        <v>18779023.107</v>
+        <v>1264128.557</v>
       </c>
     </row>
     <row r="5489">
       <c r="A5489" t="inlineStr">
         <is>
-          <t>2017-09-23</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B5489" t="n">
-        <v>18137220.352</v>
+        <v>18779023.107</v>
       </c>
     </row>
     <row r="5490">
       <c r="A5490" t="inlineStr">
         <is>
-          <t>2015-05-27</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="B5490" t="n">
-        <v>2974495.006</v>
+        <v>18137220.352</v>
       </c>
     </row>
     <row r="5491">
       <c r="A5491" t="inlineStr">
         <is>
-          <t>2014-11-05</t>
+          <t>2015-05-27</t>
         </is>
       </c>
       <c r="B5491" t="n">
-        <v>2856169.932</v>
+        <v>2974495.006</v>
       </c>
     </row>
     <row r="5492">
       <c r="A5492" t="inlineStr">
         <is>
-          <t>2014-10-23</t>
+          <t>2014-11-05</t>
         </is>
       </c>
       <c r="B5492" t="n">
-        <v>3053937.556</v>
+        <v>2856169.932</v>
       </c>
     </row>
     <row r="5493">
       <c r="A5493" t="inlineStr">
         <is>
-          <t>2022-12-22</t>
+          <t>2014-10-23</t>
         </is>
       </c>
       <c r="B5493" t="n">
-        <v>10615483.231</v>
+        <v>3053937.556</v>
       </c>
     </row>
     <row r="5494">
       <c r="A5494" t="inlineStr">
         <is>
-          <t>2012-04-01</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="B5494" t="n">
-        <v>1068036.951</v>
+        <v>10615483.231</v>
       </c>
     </row>
     <row r="5495">
       <c r="A5495" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2012-04-01</t>
         </is>
       </c>
       <c r="B5495" t="n">
-        <v>15740885.312</v>
+        <v>1068036.951</v>
       </c>
     </row>
     <row r="5496">
       <c r="A5496" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B5496" t="n">
-        <v>12796519.886</v>
+        <v>15740885.312</v>
       </c>
     </row>
     <row r="5497">
       <c r="A5497" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="B5497" t="n">
-        <v>13639848.875</v>
+        <v>12796519.886</v>
       </c>
     </row>
     <row r="5498">
       <c r="A5498" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="B5498" t="n">
-        <v>15795124.861</v>
+        <v>13639848.875</v>
       </c>
     </row>
     <row r="5499">
       <c r="A5499" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B5499" t="n">
-        <v>20455744.669</v>
+        <v>15795124.861</v>
       </c>
     </row>
     <row r="5500">
       <c r="A5500" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B5500" t="n">
-        <v>19407598.446</v>
+        <v>20455744.669</v>
       </c>
     </row>
     <row r="5501">
       <c r="A5501" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="B5501" t="n">
-        <v>22404450.46</v>
+        <v>19407598.446</v>
       </c>
     </row>
     <row r="5502">
       <c r="A5502" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B5502" t="n">
-        <v>2765454.564</v>
+        <v>22404450.46</v>
       </c>
     </row>
     <row r="5503">
       <c r="A5503" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2015-06-03</t>
         </is>
       </c>
       <c r="B5503" t="n">
-        <v>3044004.834</v>
+        <v>2765454.564</v>
       </c>
     </row>
     <row r="5504">
       <c r="A5504" t="inlineStr">
         <is>
-          <t>2014-10-01</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="B5504" t="n">
-        <v>2614443.347</v>
+        <v>3044004.834</v>
       </c>
     </row>
     <row r="5505">
       <c r="A5505" t="inlineStr">
         <is>
-          <t>2012-04-02</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="B5505" t="n">
-        <v>1066217.337</v>
+        <v>2614443.347</v>
       </c>
     </row>
     <row r="5506">
       <c r="A5506" t="inlineStr">
         <is>
-          <t>2023-01-07</t>
+          <t>2012-04-02</t>
         </is>
       </c>
       <c r="B5506" t="n">
-        <v>11376341.238</v>
+        <v>1066217.337</v>
       </c>
     </row>
     <row r="5507">
       <c r="A5507" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B5507" t="n">
-        <v>14589767.49</v>
+        <v>10477853.005</v>
       </c>
     </row>
     <row r="5508">
       <c r="A5508" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2023-01-07</t>
         </is>
       </c>
       <c r="B5508" t="n">
-        <v>13432763.242</v>
+        <v>11376341.238</v>
       </c>
     </row>
     <row r="5509">
       <c r="A5509" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B5509" t="n">
-        <v>9914365.379000001</v>
+        <v>14589767.49</v>
       </c>
     </row>
     <row r="5510">
       <c r="A5510" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B5510" t="n">
-        <v>17904427.701</v>
+        <v>13432763.242</v>
       </c>
     </row>
     <row r="5511">
       <c r="A5511" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B5511" t="n">
-        <v>19306849.276</v>
+        <v>9914365.379000001</v>
       </c>
     </row>
     <row r="5512">
       <c r="A5512" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B5512" t="n">
-        <v>2361717.899</v>
+        <v>17904427.701</v>
       </c>
     </row>
     <row r="5513">
       <c r="A5513" t="inlineStr">
         <is>
-          <t>2014-11-19</t>
+          <t>2017-10-26</t>
         </is>
       </c>
       <c r="B5513" t="n">
-        <v>3019744.611</v>
+        <v>19306849.276</v>
       </c>
     </row>
     <row r="5514">
       <c r="A5514" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2015-06-09</t>
         </is>
       </c>
       <c r="B5514" t="n">
-        <v>2896052.449</v>
+        <v>2361717.899</v>
       </c>
     </row>
     <row r="5515">
       <c r="A5515" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2014-11-19</t>
         </is>
       </c>
       <c r="B5515" t="n">
-        <v>11260943.27</v>
+        <v>3019744.611</v>
       </c>
     </row>
     <row r="5516">
       <c r="A5516" t="inlineStr">
         <is>
-          <t>2012-04-18</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="B5516" t="n">
-        <v>1080512.495</v>
+        <v>2896052.449</v>
       </c>
     </row>
     <row r="5517">
       <c r="A5517" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="B5517" t="n">
-        <v>14551069.327</v>
+        <v>11260943.27</v>
       </c>
     </row>
     <row r="5518">
       <c r="A5518" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2012-04-18</t>
         </is>
       </c>
       <c r="B5518" t="n">
-        <v>10360571.322</v>
+        <v>1080512.495</v>
       </c>
     </row>
     <row r="5519">
       <c r="A5519" t="inlineStr">
         <is>
-          <t>2021-02-12</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B5519" t="n">
-        <v>18047843.242</v>
+        <v>14551069.327</v>
       </c>
     </row>
     <row r="5520">
       <c r="A5520" t="inlineStr">
         <is>
-          <t>2017-11-16</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="B5520" t="n">
-        <v>15794441.353</v>
+        <v>10360571.322</v>
       </c>
     </row>
     <row r="5521">
       <c r="A5521" t="inlineStr">
         <is>
-          <t>2015-06-16</t>
+          <t>2021-02-12</t>
         </is>
       </c>
       <c r="B5521" t="n">
-        <v>2394815.633</v>
+        <v>18047843.242</v>
       </c>
     </row>
     <row r="5522">
       <c r="A5522" t="inlineStr">
         <is>
-          <t>2014-12-05</t>
+          <t>2017-11-16</t>
         </is>
       </c>
       <c r="B5522" t="n">
-        <v>3374566.02</v>
+        <v>15794441.353</v>
       </c>
     </row>
     <row r="5523">
       <c r="A5523" t="inlineStr">
         <is>
-          <t>2014-08-03</t>
+          <t>2015-06-16</t>
         </is>
       </c>
       <c r="B5523" t="n">
-        <v>2623351.252</v>
+        <v>2394815.633</v>
       </c>
     </row>
     <row r="5524">
       <c r="A5524" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2014-12-05</t>
         </is>
       </c>
       <c r="B5524" t="n">
-        <v>7804497.859</v>
+        <v>3374566.02</v>
       </c>
     </row>
     <row r="5525">
       <c r="A5525" t="inlineStr">
         <is>
-          <t>2012-05-04</t>
+          <t>2014-08-03</t>
         </is>
       </c>
       <c r="B5525" t="n">
-        <v>1211448.82</v>
+        <v>2623351.252</v>
       </c>
     </row>
     <row r="5526">
       <c r="A5526" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="B5526" t="n">
-        <v>9388382.575999999</v>
+        <v>7804497.859</v>
       </c>
     </row>
     <row r="5527">
       <c r="A5527" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2012-05-04</t>
         </is>
       </c>
       <c r="B5527" t="n">
-        <v>9877779.377</v>
+        <v>1211448.82</v>
       </c>
     </row>
     <row r="5528">
       <c r="A5528" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B5528" t="n">
-        <v>10504922.862</v>
+        <v>9388382.575999999</v>
       </c>
     </row>
     <row r="5529">
       <c r="A5529" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B5529" t="n">
-        <v>17461848.264</v>
+        <v>9877779.377</v>
       </c>
     </row>
     <row r="5530">
       <c r="A5530" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="B5530" t="n">
-        <v>15739620.059</v>
+        <v>10504922.862</v>
       </c>
     </row>
     <row r="5531">
       <c r="A5531" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B5531" t="n">
-        <v>2573704.983</v>
+        <v>17461848.264</v>
       </c>
     </row>
     <row r="5532">
       <c r="A5532" t="inlineStr">
         <is>
-          <t>2014-12-24</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="B5532" t="n">
-        <v>3749367.14</v>
+        <v>15739620.059</v>
       </c>
     </row>
     <row r="5533">
       <c r="A5533" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="B5533" t="n">
-        <v>2593413.479</v>
+        <v>2573704.983</v>
       </c>
     </row>
     <row r="5534">
       <c r="A5534" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2014-12-24</t>
         </is>
       </c>
       <c r="B5534" t="n">
-        <v>18609730.033</v>
+        <v>3749367.14</v>
       </c>
     </row>
     <row r="5535">
       <c r="A5535" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2014-07-09</t>
         </is>
       </c>
       <c r="B5535" t="n">
-        <v>7349744.434</v>
+        <v>2593413.479</v>
       </c>
     </row>
     <row r="5536">
       <c r="A5536" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B5536" t="n">
-        <v>1258763.689</v>
+        <v>18609730.033</v>
       </c>
     </row>
     <row r="5537">
       <c r="A5537" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="B5537" t="n">
-        <v>15643923.15</v>
+        <v>7349744.434</v>
       </c>
     </row>
     <row r="5538">
       <c r="A5538" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="B5538" t="n">
-        <v>18799096.649</v>
+        <v>1258763.689</v>
       </c>
     </row>
     <row r="5539">
       <c r="A5539" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B5539" t="n">
-        <v>10857484.275</v>
+        <v>15643923.15</v>
       </c>
     </row>
     <row r="5540">
       <c r="A5540" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B5540" t="n">
-        <v>11149234.035</v>
+        <v>18799096.649</v>
       </c>
     </row>
     <row r="5541">
       <c r="A5541" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B5541" t="n">
-        <v>15621689.103</v>
+        <v>10857484.275</v>
       </c>
     </row>
     <row r="5542">
       <c r="A5542" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="B5542" t="n">
-        <v>15009732.42</v>
+        <v>11149234.035</v>
       </c>
     </row>
     <row r="5543">
       <c r="A5543" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="B5543" t="n">
-        <v>15786676.067</v>
+        <v>15621689.103</v>
       </c>
     </row>
     <row r="5544">
       <c r="A5544" t="inlineStr">
         <is>
-          <t>2015-07-01</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B5544" t="n">
-        <v>2511092.261</v>
+        <v>15009732.42</v>
       </c>
     </row>
     <row r="5545">
       <c r="A5545" t="inlineStr">
         <is>
-          <t>2015-01-11</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="B5545" t="n">
-        <v>3848375.44</v>
+        <v>15786676.067</v>
       </c>
     </row>
     <row r="5546">
       <c r="A5546" t="inlineStr">
         <is>
-          <t>2014-06-19</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="B5546" t="n">
-        <v>2739682.925</v>
+        <v>2511092.261</v>
       </c>
     </row>
     <row r="5547">
       <c r="A5547" t="inlineStr">
         <is>
-          <t>2012-06-06</t>
+          <t>2015-01-11</t>
         </is>
       </c>
       <c r="B5547" t="n">
-        <v>1365675.341</v>
+        <v>3848375.44</v>
       </c>
     </row>
     <row r="5548">
       <c r="A5548" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2014-06-19</t>
         </is>
       </c>
       <c r="B5548" t="n">
-        <v>8127301.046</v>
+        <v>2739682.925</v>
       </c>
     </row>
     <row r="5549">
       <c r="A5549" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2012-06-06</t>
         </is>
       </c>
       <c r="B5549" t="n">
-        <v>14446234.788</v>
+        <v>1365675.341</v>
       </c>
     </row>
     <row r="5550">
       <c r="A5550" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="B5550" t="n">
-        <v>18209088.114</v>
+        <v>8127301.046</v>
       </c>
     </row>
     <row r="5551">
       <c r="A5551" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B5551" t="n">
-        <v>10805935.58</v>
+        <v>14446234.788</v>
       </c>
     </row>
     <row r="5552">
       <c r="A5552" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B5552" t="n">
-        <v>22365594.535</v>
+        <v>18209088.114</v>
       </c>
     </row>
     <row r="5553">
       <c r="A5553" t="inlineStr">
         <is>
-          <t>2021-05-09</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="B5553" t="n">
-        <v>13264526.584</v>
+        <v>10805935.58</v>
       </c>
     </row>
     <row r="5554">
       <c r="A5554" t="inlineStr">
         <is>
-          <t>2017-12-18</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B5554" t="n">
-        <v>17645156.999</v>
+        <v>22365594.535</v>
       </c>
     </row>
     <row r="5555">
       <c r="A5555" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-05-09</t>
         </is>
       </c>
       <c r="B5555" t="n">
-        <v>2718554.466</v>
+        <v>13264526.584</v>
       </c>
     </row>
     <row r="5556">
       <c r="A5556" t="inlineStr">
         <is>
-          <t>2015-01-20</t>
+          <t>2017-12-18</t>
         </is>
       </c>
       <c r="B5556" t="n">
-        <v>4046018.483</v>
+        <v>17645156.999</v>
       </c>
     </row>
     <row r="5557">
       <c r="A5557" t="inlineStr">
         <is>
-          <t>2014-05-27</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="B5557" t="n">
-        <v>4448327.388</v>
+        <v>2718554.466</v>
       </c>
     </row>
     <row r="5558">
       <c r="A5558" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2015-01-20</t>
         </is>
       </c>
       <c r="B5558" t="n">
-        <v>8486747.433</v>
+        <v>4046018.483</v>
       </c>
     </row>
     <row r="5559">
       <c r="A5559" t="inlineStr">
         <is>
-          <t>2012-06-18</t>
+          <t>2014-05-27</t>
         </is>
       </c>
       <c r="B5559" t="n">
-        <v>1367243.39</v>
+        <v>4448327.388</v>
       </c>
     </row>
     <row r="5560">
       <c r="A5560" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="B5560" t="n">
-        <v>14010038.153</v>
+        <v>8486747.433</v>
       </c>
     </row>
     <row r="5561">
       <c r="A5561" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2012-06-18</t>
         </is>
       </c>
       <c r="B5561" t="n">
-        <v>12870879.477</v>
+        <v>1367243.39</v>
       </c>
     </row>
     <row r="5562">
       <c r="A5562" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5562" t="n">
-        <v>15346852.871</v>
+        <v>14010038.153</v>
       </c>
     </row>
     <row r="5563">
       <c r="A5563" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B5563" t="n">
-        <v>9114476.312000001</v>
+        <v>12870879.477</v>
       </c>
     </row>
     <row r="5564">
       <c r="A5564" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B5564" t="n">
-        <v>10847808.277</v>
+        <v>15346852.871</v>
       </c>
     </row>
     <row r="5565">
       <c r="A5565" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B5565" t="n">
-        <v>22259727.582</v>
+        <v>9114476.312000001</v>
       </c>
     </row>
     <row r="5566">
       <c r="A5566" t="inlineStr">
         <is>
-          <t>2021-05-15</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="B5566" t="n">
-        <v>13194431.726</v>
+        <v>10847808.277</v>
       </c>
     </row>
     <row r="5567">
       <c r="A5567" t="inlineStr">
         <is>
-          <t>2018-01-06</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B5567" t="n">
-        <v>17780525.245</v>
+        <v>22259727.582</v>
       </c>
     </row>
     <row r="5568">
       <c r="A5568" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
+          <t>2021-05-15</t>
         </is>
       </c>
       <c r="B5568" t="n">
-        <v>2793932.294</v>
+        <v>13194431.726</v>
       </c>
     </row>
     <row r="5569">
       <c r="A5569" t="inlineStr">
         <is>
-          <t>2015-02-10</t>
+          <t>2018-01-06</t>
         </is>
       </c>
       <c r="B5569" t="n">
-        <v>4071380.974</v>
+        <v>17780525.245</v>
       </c>
     </row>
     <row r="5570">
       <c r="A5570" t="inlineStr">
         <is>
-          <t>2014-05-10</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="B5570" t="n">
-        <v>4403960.45</v>
+        <v>2793932.294</v>
       </c>
     </row>
     <row r="5571">
       <c r="A5571" t="inlineStr">
         <is>
-          <t>2012-06-28</t>
+          <t>2015-02-10</t>
         </is>
       </c>
       <c r="B5571" t="n">
-        <v>1363857.943</v>
+        <v>4071380.974</v>
       </c>
     </row>
     <row r="5572">
       <c r="A5572" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2014-05-10</t>
         </is>
       </c>
       <c r="B5572" t="n">
-        <v>17968690.541</v>
+        <v>4403960.45</v>
       </c>
     </row>
     <row r="5573">
       <c r="A5573" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2012-06-28</t>
         </is>
       </c>
       <c r="B5573" t="n">
-        <v>8346328.634</v>
+        <v>1363857.943</v>
       </c>
     </row>
     <row r="5574">
       <c r="A5574" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B5574" t="n">
-        <v>18882222.042</v>
+        <v>17968690.541</v>
       </c>
     </row>
     <row r="5575">
       <c r="A5575" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="B5575" t="n">
-        <v>9386582.370999999</v>
+        <v>8346328.634</v>
       </c>
     </row>
     <row r="5576">
       <c r="A5576" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="B5576" t="n">
-        <v>10773183.386</v>
+        <v>18882222.042</v>
       </c>
     </row>
     <row r="5577">
       <c r="A5577" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B5577" t="n">
-        <v>16585261.576</v>
+        <v>9386582.370999999</v>
       </c>
     </row>
     <row r="5578">
       <c r="A5578" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B5578" t="n">
-        <v>16236706.926</v>
+        <v>10773183.386</v>
       </c>
     </row>
     <row r="5579">
       <c r="A5579" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="B5579" t="n">
-        <v>21808754.591</v>
+        <v>16585261.576</v>
       </c>
     </row>
     <row r="5580">
       <c r="A5580" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="B5580" t="n">
-        <v>12015164.279</v>
+        <v>16236706.926</v>
       </c>
     </row>
     <row r="5581">
       <c r="A5581" t="inlineStr">
         <is>
-          <t>2018-01-18</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B5581" t="n">
-        <v>17890389.899</v>
+        <v>21808754.591</v>
       </c>
     </row>
     <row r="5582">
       <c r="A5582" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="B5582" t="n">
-        <v>2826416.003</v>
+        <v>12015164.279</v>
       </c>
     </row>
     <row r="5583">
       <c r="A5583" t="inlineStr">
         <is>
-          <t>2015-02-26</t>
+          <t>2018-01-18</t>
         </is>
       </c>
       <c r="B5583" t="n">
-        <v>3819509.271</v>
+        <v>17890389.899</v>
       </c>
     </row>
     <row r="5584">
       <c r="A5584" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2015-07-24</t>
         </is>
       </c>
       <c r="B5584" t="n">
-        <v>20554065.145</v>
+        <v>2826416.003</v>
       </c>
     </row>
     <row r="5585">
       <c r="A5585" t="inlineStr">
         <is>
-          <t>2014-04-26</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="B5585" t="n">
-        <v>5460076.352</v>
+        <v>3819509.271</v>
       </c>
     </row>
     <row r="5586">
       <c r="A5586" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B5586" t="n">
-        <v>7902657.124</v>
+        <v>20554065.145</v>
       </c>
     </row>
     <row r="5587">
       <c r="A5587" t="inlineStr">
         <is>
-          <t>2012-07-21</t>
+          <t>2014-04-26</t>
         </is>
       </c>
       <c r="B5587" t="n">
-        <v>1630324.679</v>
+        <v>5460076.352</v>
       </c>
     </row>
     <row r="5588">
       <c r="A5588" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="B5588" t="n">
-        <v>14252744.065</v>
+        <v>7902657.124</v>
       </c>
     </row>
     <row r="5589">
       <c r="A5589" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2012-07-21</t>
         </is>
       </c>
       <c r="B5589" t="n">
-        <v>10658742.561</v>
+        <v>1630324.679</v>
       </c>
     </row>
     <row r="5590">
       <c r="A5590" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B5590" t="n">
-        <v>18727823.649</v>
+        <v>14252744.065</v>
       </c>
     </row>
     <row r="5591">
       <c r="A5591" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B5591" t="n">
-        <v>10503343.65</v>
+        <v>10658742.561</v>
       </c>
     </row>
     <row r="5592">
       <c r="A5592" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B5592" t="n">
-        <v>10785349.848</v>
+        <v>18727823.649</v>
       </c>
     </row>
     <row r="5593">
       <c r="A5593" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B5593" t="n">
-        <v>10673931.348</v>
+        <v>10503343.65</v>
       </c>
     </row>
     <row r="5594">
       <c r="A5594" t="inlineStr">
         <is>
-          <t>2018-01-31</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B5594" t="n">
-        <v>17224052.503</v>
+        <v>10785349.848</v>
       </c>
     </row>
     <row r="5595">
       <c r="A5595" t="inlineStr">
         <is>
-          <t>2015-10-14</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="B5595" t="n">
-        <v>3642872.298</v>
+        <v>10673931.348</v>
       </c>
     </row>
     <row r="5596">
       <c r="A5596" t="inlineStr">
         <is>
-          <t>2015-03-25</t>
+          <t>2018-01-31</t>
         </is>
       </c>
       <c r="B5596" t="n">
-        <v>3979751.142</v>
+        <v>17224052.503</v>
       </c>
     </row>
     <row r="5597">
       <c r="A5597" t="inlineStr">
         <is>
-          <t>2014-04-16</t>
+          <t>2015-10-14</t>
         </is>
       </c>
       <c r="B5597" t="n">
-        <v>5493117.057</v>
+        <v>3642872.298</v>
       </c>
     </row>
     <row r="5598">
       <c r="A5598" t="inlineStr">
         <is>
-          <t>2012-08-07</t>
+          <t>2015-03-25</t>
         </is>
       </c>
       <c r="B5598" t="n">
-        <v>1613219.441</v>
+        <v>3979751.142</v>
       </c>
     </row>
     <row r="5599">
       <c r="A5599" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2014-04-16</t>
         </is>
       </c>
       <c r="B5599" t="n">
-        <v>18803774.412</v>
+        <v>5493117.057</v>
       </c>
     </row>
     <row r="5600">
       <c r="A5600" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2012-08-07</t>
         </is>
       </c>
       <c r="B5600" t="n">
-        <v>18746833.543</v>
+        <v>1613219.441</v>
       </c>
     </row>
     <row r="5601">
       <c r="A5601" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B5601" t="n">
-        <v>14696488.122</v>
+        <v>18803774.412</v>
       </c>
     </row>
     <row r="5602">
       <c r="A5602" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B5602" t="n">
-        <v>13074131.781</v>
+        <v>18746833.543</v>
       </c>
     </row>
     <row r="5603">
       <c r="A5603" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B5603" t="n">
-        <v>11136369.663</v>
+        <v>14696488.122</v>
       </c>
     </row>
     <row r="5604">
       <c r="A5604" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B5604" t="n">
-        <v>22620694.513</v>
+        <v>13074131.781</v>
       </c>
     </row>
     <row r="5605">
       <c r="A5605" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="B5605" t="n">
-        <v>10600975.162</v>
+        <v>11136369.663</v>
       </c>
     </row>
     <row r="5606">
       <c r="A5606" t="inlineStr">
         <is>
-          <t>2018-02-07</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B5606" t="n">
-        <v>18108889.119</v>
+        <v>22620694.513</v>
       </c>
     </row>
     <row r="5607">
       <c r="A5607" t="inlineStr">
         <is>
-          <t>2015-10-20</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="B5607" t="n">
-        <v>3660667.082</v>
+        <v>10600975.162</v>
       </c>
     </row>
     <row r="5608">
       <c r="A5608" t="inlineStr">
         <is>
-          <t>2015-04-15</t>
+          <t>2018-02-07</t>
         </is>
       </c>
       <c r="B5608" t="n">
-        <v>3489354.733</v>
+        <v>18108889.119</v>
       </c>
     </row>
     <row r="5609">
       <c r="A5609" t="inlineStr">
         <is>
-          <t>2010-11-29</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="B5609" t="n">
-        <v>316907.127</v>
+        <v>3660667.082</v>
       </c>
     </row>
     <row r="5610">
       <c r="A5610" t="inlineStr">
         <is>
-          <t>2014-03-26</t>
+          <t>2015-04-15</t>
         </is>
       </c>
       <c r="B5610" t="n">
-        <v>5421476.718</v>
+        <v>3489354.733</v>
       </c>
     </row>
     <row r="5611">
       <c r="A5611" t="inlineStr">
         <is>
-          <t>2012-08-23</t>
+          <t>2010-11-29</t>
         </is>
       </c>
       <c r="B5611" t="n">
-        <v>1760535.998</v>
+        <v>316907.127</v>
       </c>
     </row>
     <row r="5612">
       <c r="A5612" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2014-03-26</t>
         </is>
       </c>
       <c r="B5612" t="n">
-        <v>19760413.223</v>
+        <v>5421476.718</v>
       </c>
     </row>
     <row r="5613">
       <c r="A5613" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="B5613" t="n">
-        <v>11420107.846</v>
+        <v>1760535.998</v>
       </c>
     </row>
     <row r="5614">
       <c r="A5614" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B5614" t="n">
-        <v>10677343.165</v>
+        <v>19760413.223</v>
       </c>
     </row>
     <row r="5615">
       <c r="A5615" t="inlineStr">
         <is>
-          <t>2018-02-17</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="B5615" t="n">
-        <v>15296257.118</v>
+        <v>11420107.846</v>
       </c>
     </row>
     <row r="5616">
       <c r="A5616" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="B5616" t="n">
-        <v>4648212.458</v>
+        <v>10677343.165</v>
       </c>
     </row>
     <row r="5617">
       <c r="A5617" t="inlineStr">
         <is>
-          <t>2015-05-16</t>
+          <t>2018-02-17</t>
         </is>
       </c>
       <c r="B5617" t="n">
-        <v>3205484.527</v>
+        <v>15296257.118</v>
       </c>
     </row>
     <row r="5618">
       <c r="A5618" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="B5618" t="n">
-        <v>4848958.836</v>
+        <v>4648212.458</v>
       </c>
     </row>
     <row r="5619">
       <c r="A5619" t="inlineStr">
         <is>
-          <t>2012-09-08</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="B5619" t="n">
-        <v>1873037.142</v>
+        <v>3205484.527</v>
       </c>
     </row>
     <row r="5620">
       <c r="A5620" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="B5620" t="n">
-        <v>12841467.318</v>
+        <v>4848958.836</v>
       </c>
     </row>
     <row r="5621">
       <c r="A5621" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2012-09-08</t>
         </is>
       </c>
       <c r="B5621" t="n">
-        <v>19272529.034</v>
+        <v>1873037.142</v>
       </c>
     </row>
     <row r="5622">
       <c r="A5622" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B5622" t="n">
-        <v>11384746.006</v>
+        <v>12841467.318</v>
       </c>
     </row>
     <row r="5623">
       <c r="A5623" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B5623" t="n">
-        <v>8610177.493000001</v>
+        <v>19272529.034</v>
       </c>
     </row>
     <row r="5624">
       <c r="A5624" t="inlineStr">
         <is>
-          <t>2018-03-09</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B5624" t="n">
-        <v>13193422.783</v>
+        <v>11384746.006</v>
       </c>
     </row>
     <row r="5625">
       <c r="A5625" t="inlineStr">
         <is>
-          <t>2015-12-09</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="B5625" t="n">
-        <v>4603582.061</v>
+        <v>8610177.493000001</v>
       </c>
     </row>
     <row r="5626">
       <c r="A5626" t="inlineStr">
         <is>
-          <t>2015-05-28</t>
+          <t>2018-03-09</t>
         </is>
       </c>
       <c r="B5626" t="n">
-        <v>2985205.142</v>
+        <v>13193422.783</v>
       </c>
     </row>
     <row r="5627">
       <c r="A5627" t="inlineStr">
         <is>
-          <t>2014-01-27</t>
+          <t>2015-12-09</t>
         </is>
       </c>
       <c r="B5627" t="n">
-        <v>6138612.726</v>
+        <v>4603582.061</v>
       </c>
     </row>
     <row r="5628">
       <c r="A5628" t="inlineStr">
         <is>
-          <t>2012-09-24</t>
+          <t>2015-05-28</t>
         </is>
       </c>
       <c r="B5628" t="n">
-        <v>2093652.744</v>
+        <v>2985205.142</v>
       </c>
     </row>
     <row r="5629">
       <c r="A5629" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2014-01-27</t>
         </is>
       </c>
       <c r="B5629" t="n">
-        <v>19496972.836</v>
+        <v>6138612.726</v>
       </c>
     </row>
     <row r="5630">
       <c r="A5630" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2012-09-24</t>
         </is>
       </c>
       <c r="B5630" t="n">
-        <v>12225489.867</v>
+        <v>2093652.744</v>
       </c>
     </row>
     <row r="5631">
       <c r="A5631" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B5631" t="n">
-        <v>11477197.525</v>
+        <v>19496972.836</v>
       </c>
     </row>
     <row r="5632">
       <c r="A5632" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B5632" t="n">
-        <v>11313913.816</v>
+        <v>12225489.867</v>
       </c>
     </row>
     <row r="5633">
       <c r="A5633" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="B5633" t="n">
-        <v>18346710.052</v>
+        <v>11477197.525</v>
       </c>
     </row>
     <row r="5634">
       <c r="A5634" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B5634" t="n">
-        <v>8609734.759</v>
+        <v>11313913.816</v>
       </c>
     </row>
     <row r="5635">
       <c r="A5635" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B5635" t="n">
-        <v>10566019.663</v>
+        <v>18346710.052</v>
       </c>
     </row>
     <row r="5636">
       <c r="A5636" t="inlineStr">
         <is>
-          <t>2015-12-18</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="B5636" t="n">
-        <v>4964683.773</v>
+        <v>8609734.759</v>
       </c>
     </row>
     <row r="5637">
       <c r="A5637" t="inlineStr">
         <is>
-          <t>2015-06-12</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="B5637" t="n">
-        <v>2392944.256</v>
+        <v>10566019.663</v>
       </c>
     </row>
     <row r="5638">
       <c r="A5638" t="inlineStr">
         <is>
-          <t>2013-12-31</t>
+          <t>2015-12-18</t>
         </is>
       </c>
       <c r="B5638" t="n">
-        <v>6890936.406</v>
+        <v>4964683.773</v>
       </c>
     </row>
     <row r="5639">
       <c r="A5639" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="B5639" t="n">
-        <v>2162784.464</v>
+        <v>2392944.256</v>
       </c>
     </row>
     <row r="5640">
       <c r="A5640" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2013-12-31</t>
         </is>
       </c>
       <c r="B5640" t="n">
-        <v>18616838.388</v>
+        <v>6890936.406</v>
       </c>
     </row>
     <row r="5641">
       <c r="A5641" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="B5641" t="n">
-        <v>16688077.13</v>
+        <v>2162784.464</v>
       </c>
     </row>
     <row r="5642">
       <c r="A5642" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B5642" t="n">
-        <v>19740398.471</v>
+        <v>18616838.388</v>
       </c>
     </row>
     <row r="5643">
       <c r="A5643" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B5643" t="n">
-        <v>8443126.151000001</v>
+        <v>16688077.13</v>
       </c>
     </row>
     <row r="5644">
       <c r="A5644" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B5644" t="n">
-        <v>8046257.588</v>
+        <v>19740398.471</v>
       </c>
     </row>
     <row r="5645">
       <c r="A5645" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="B5645" t="n">
-        <v>6127123.106</v>
+        <v>8443126.151000001</v>
       </c>
     </row>
     <row r="5646">
       <c r="A5646" t="inlineStr">
         <is>
-          <t>2015-07-04</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="B5646" t="n">
-        <v>2565551.236</v>
+        <v>8046257.588</v>
       </c>
     </row>
     <row r="5647">
       <c r="A5647" t="inlineStr">
         <is>
-          <t>2013-12-05</t>
+          <t>2016-04-20</t>
         </is>
       </c>
       <c r="B5647" t="n">
-        <v>5651552.322</v>
+        <v>6127123.106</v>
       </c>
     </row>
     <row r="5648">
       <c r="A5648" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2015-07-04</t>
         </is>
       </c>
       <c r="B5648" t="n">
-        <v>8386250.008</v>
+        <v>2565551.236</v>
       </c>
     </row>
     <row r="5649">
       <c r="A5649" t="inlineStr">
         <is>
-          <t>2012-10-27</t>
+          <t>2013-12-05</t>
         </is>
       </c>
       <c r="B5649" t="n">
-        <v>2157212.824</v>
+        <v>5651552.322</v>
       </c>
     </row>
     <row r="5650">
       <c r="A5650" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="B5650" t="n">
-        <v>15303734.889</v>
+        <v>8386250.008</v>
       </c>
     </row>
     <row r="5651">
       <c r="A5651" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2012-10-27</t>
         </is>
       </c>
       <c r="B5651" t="n">
-        <v>11978202.448</v>
+        <v>2157212.824</v>
       </c>
     </row>
     <row r="5652">
       <c r="A5652" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B5652" t="n">
-        <v>16127948.086</v>
+        <v>15303734.889</v>
       </c>
     </row>
     <row r="5653">
       <c r="A5653" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B5653" t="n">
-        <v>19006487.04</v>
+        <v>11978202.448</v>
       </c>
     </row>
     <row r="5654">
       <c r="A5654" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B5654" t="n">
-        <v>9382181.960999999</v>
+        <v>16127948.086</v>
       </c>
     </row>
     <row r="5655">
       <c r="A5655" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B5655" t="n">
-        <v>8103908.652</v>
+        <v>19006487.04</v>
       </c>
     </row>
     <row r="5656">
       <c r="A5656" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="B5656" t="n">
-        <v>5532498.781</v>
+        <v>9382181.960999999</v>
       </c>
     </row>
     <row r="5657">
       <c r="A5657" t="inlineStr">
         <is>
-          <t>2015-08-03</t>
+          <t>2018-05-03</t>
         </is>
       </c>
       <c r="B5657" t="n">
-        <v>2859270.317</v>
+        <v>8103908.652</v>
       </c>
     </row>
     <row r="5658">
       <c r="A5658" t="inlineStr">
         <is>
-          <t>2013-11-19</t>
+          <t>2016-05-04</t>
         </is>
       </c>
       <c r="B5658" t="n">
-        <v>4340422.8</v>
+        <v>5532498.781</v>
       </c>
     </row>
     <row r="5659">
       <c r="A5659" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2015-08-03</t>
         </is>
       </c>
       <c r="B5659" t="n">
-        <v>17569350.656</v>
+        <v>2859270.317</v>
       </c>
     </row>
     <row r="5660">
       <c r="A5660" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2013-11-19</t>
         </is>
       </c>
       <c r="B5660" t="n">
-        <v>17249482.25</v>
+        <v>4340422.8</v>
       </c>
     </row>
     <row r="5661">
       <c r="A5661" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B5661" t="n">
-        <v>17225229.436</v>
+        <v>17569350.656</v>
       </c>
     </row>
     <row r="5662">
       <c r="A5662" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B5662" t="n">
-        <v>17153769.299</v>
+        <v>17249482.25</v>
       </c>
     </row>
     <row r="5663">
       <c r="A5663" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B5663" t="n">
-        <v>17115867.282</v>
+        <v>17225229.436</v>
       </c>
     </row>
     <row r="5664">
       <c r="A5664" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B5664" t="n">
-        <v>17049245.734</v>
+        <v>17153769.299</v>
       </c>
     </row>
     <row r="5665">
       <c r="A5665" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B5665" t="n">
-        <v>16833063.951</v>
+        <v>17115867.282</v>
       </c>
     </row>
     <row r="5666">
       <c r="A5666" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="B5666" t="n">
-        <v>16784620.262</v>
+        <v>17049245.734</v>
       </c>
     </row>
     <row r="5667">
       <c r="A5667" t="inlineStr">
         <is>
-          <t>2012-11-12</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="B5667" t="n">
-        <v>2138609.994</v>
+        <v>16833063.951</v>
       </c>
     </row>
     <row r="5668">
       <c r="A5668" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B5668" t="n">
-        <v>12895454.923</v>
+        <v>16784620.262</v>
       </c>
     </row>
     <row r="5669">
       <c r="A5669" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2012-11-12</t>
         </is>
       </c>
       <c r="B5669" t="n">
-        <v>11691372.317</v>
+        <v>2138609.994</v>
       </c>
     </row>
     <row r="5670">
       <c r="A5670" t="inlineStr">
         <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B5670" t="n">
+        <v>12895454.923</v>
+      </c>
+    </row>
+    <row r="5671">
+      <c r="A5671" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="B5671" t="n">
+        <v>11691372.317</v>
+      </c>
+    </row>
+    <row r="5672">
+      <c r="A5672" t="inlineStr">
+        <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="B5670" t="n">
+      <c r="B5672" t="n">
         <v>16110702.506</v>
       </c>
     </row>

--- a/data_cripto/btc_cdd.xlsx
+++ b/data_cripto/btc_cdd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1456"/>
+  <dimension ref="A1:B1455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12041,2950 +12041,2940 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>2022-05-03</t>
+          <t>2022-11-26</t>
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>8218318.752</v>
+        <v>10362802.579</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>2022-11-26</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>10362802.579</v>
+        <v>6153661.361</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="B1164" t="n">
-        <v>6153661.361</v>
+        <v>6190194.949</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="B1165" t="n">
-        <v>6190194.949</v>
+        <v>9874969.986</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="B1166" t="n">
-        <v>9874969.986</v>
+        <v>9880601.411</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>9880601.411</v>
+        <v>16777254.692</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>16777254.692</v>
+        <v>12798520.113</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>12798520.113</v>
+        <v>12614002.689</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>12614002.689</v>
+        <v>17508953.532</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>17508953.532</v>
+        <v>18944691.526</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="B1172" t="n">
-        <v>18944691.526</v>
+        <v>13539397.76</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>13539397.76</v>
+        <v>16908871.181</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>16908871.181</v>
+        <v>8145459.209</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>8145459.209</v>
+        <v>12536685.09</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>12536685.09</v>
+        <v>11570457.865</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>11570457.865</v>
+        <v>11463487.194</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>11463487.194</v>
+        <v>16742051.234</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B1179" t="n">
-        <v>16742051.234</v>
+        <v>17420607.699</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>17420607.699</v>
+        <v>10154290.861</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>10154290.861</v>
+        <v>18283375.171</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>18283375.171</v>
+        <v>20197508.371</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>20197508.371</v>
+        <v>13198740.126</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>13198740.126</v>
+        <v>7391634.265</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B1185" t="n">
-        <v>7391634.265</v>
+        <v>19324380.182</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B1186" t="n">
-        <v>19324380.182</v>
+        <v>18518628.999</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B1187" t="n">
-        <v>18518628.999</v>
+        <v>11533542.22</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B1188" t="n">
-        <v>11533542.22</v>
+        <v>11982419.652</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B1189" t="n">
-        <v>11982419.652</v>
+        <v>16662741.532</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>16662741.532</v>
+        <v>10165678.695</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B1191" t="n">
-        <v>10165678.695</v>
+        <v>15762243.002</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>15762243.002</v>
+        <v>13742960</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="B1193" t="n">
-        <v>13742960</v>
+        <v>6889732.972</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>6889732.972</v>
+        <v>17921349.452</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>17921349.452</v>
+        <v>11890718.505</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B1196" t="n">
-        <v>11890718.505</v>
+        <v>12190152.036</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B1197" t="n">
-        <v>12190152.036</v>
+        <v>19240581.039</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>19240581.039</v>
+        <v>15843658.658</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="B1199" t="n">
-        <v>15843658.658</v>
+        <v>7680678.394</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>7680678.394</v>
+        <v>13422882.236</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B1201" t="n">
-        <v>13422882.236</v>
+        <v>13888250.184</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="B1202" t="n">
-        <v>13888250.184</v>
+        <v>19799814.996</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>19799814.996</v>
+        <v>16092268.729</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="B1204" t="n">
-        <v>16092268.729</v>
+        <v>19077349.963</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="B1205" t="n">
-        <v>19077349.963</v>
+        <v>7424064.951</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>2023-03-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B1206" t="n">
-        <v>7424064.951</v>
+        <v>13449347.64</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="B1207" t="n">
-        <v>13449347.64</v>
+        <v>19554838.811</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-01-08</t>
         </is>
       </c>
       <c r="B1208" t="n">
-        <v>19554838.811</v>
+        <v>11379536.421</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>2023-01-08</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B1209" t="n">
-        <v>11379536.421</v>
+        <v>18061928.338</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B1210" t="n">
-        <v>18061928.338</v>
+        <v>18195056.999</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B1211" t="n">
-        <v>18195056.999</v>
+        <v>20311437.78</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B1212" t="n">
-        <v>20311437.78</v>
+        <v>19921671.37</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B1213" t="n">
-        <v>19921671.37</v>
+        <v>10139727.84</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>10139727.84</v>
+        <v>15736728.197</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>15736728.197</v>
+        <v>8237636.144</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>8237636.144</v>
+        <v>10034680.589</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>10034680.589</v>
+        <v>19912305.448</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-01-05</t>
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>19912305.448</v>
+        <v>11252026.475</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B1219" t="n">
-        <v>11252026.475</v>
+        <v>16368609.325</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>16368609.325</v>
+        <v>13010963.419</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>13010963.419</v>
+        <v>15408192.117</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>15408192.117</v>
+        <v>17931313.804</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>17931313.804</v>
+        <v>10313035.77</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>10313035.77</v>
+        <v>13202621.428</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B1225" t="n">
-        <v>13202621.428</v>
+        <v>8301700.833</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>8301700.833</v>
+        <v>17680988.152</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="B1227" t="n">
-        <v>17680988.152</v>
+        <v>7860090.304</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>7860090.304</v>
+        <v>14555529.314</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B1229" t="n">
-        <v>14555529.314</v>
+        <v>9250585.187000001</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>9250585.187000001</v>
+        <v>17316630.871</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>17316630.871</v>
+        <v>9643468.957</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>9643468.957</v>
+        <v>22762705.257</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B1233" t="n">
-        <v>22762705.257</v>
+        <v>15903527.022</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B1234" t="n">
-        <v>15903527.022</v>
+        <v>14080491.729</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B1235" t="n">
-        <v>14080491.729</v>
+        <v>9348543.609999999</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B1236" t="n">
-        <v>9348543.609999999</v>
+        <v>9876625.647</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="B1237" t="n">
-        <v>9876625.647</v>
+        <v>16658702.812</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2022-05-14</t>
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>16658702.812</v>
+        <v>9471646.251</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>9471646.251</v>
+        <v>15559579.28</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>15559579.28</v>
+        <v>11176294.018</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>11176294.018</v>
+        <v>15649596.102</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B1242" t="n">
-        <v>15649596.102</v>
+        <v>22213431.033</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B1243" t="n">
-        <v>22213431.033</v>
+        <v>14548570.861</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>14548570.861</v>
+        <v>18413104.776</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B1245" t="n">
-        <v>18413104.776</v>
+        <v>10785396.841</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>10785396.841</v>
+        <v>20506438.825</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>20506438.825</v>
+        <v>8310304.394</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>8310304.394</v>
+        <v>8698898.304</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>8698898.304</v>
+        <v>8799800.285</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>8799800.285</v>
+        <v>19218055.445</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>19218055.445</v>
+        <v>14601308.011</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>14601308.011</v>
+        <v>12724123.607</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>12724123.607</v>
+        <v>14880148.605</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="B1254" t="n">
-        <v>14880148.605</v>
+        <v>9252340.935000001</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>9252340.935000001</v>
+        <v>8671524.054</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>8671524.054</v>
+        <v>18218036.776</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B1257" t="n">
-        <v>18218036.776</v>
+        <v>18095870.058</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>18095870.058</v>
+        <v>19014663.42</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B1259" t="n">
-        <v>19014663.42</v>
+        <v>9408798.934</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>9408798.934</v>
+        <v>16670126.739</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>16670126.739</v>
+        <v>16265749.775</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>16265749.775</v>
+        <v>8297333.426</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>8297333.426</v>
+        <v>21748228.097</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B1264" t="n">
-        <v>21748228.097</v>
+        <v>15610517.939</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B1265" t="n">
-        <v>15610517.939</v>
+        <v>18752011.913</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>18752011.913</v>
+        <v>10512254.974</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>10512254.974</v>
+        <v>18684510.463</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B1268" t="n">
-        <v>18684510.463</v>
+        <v>10958641.073</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>10958641.073</v>
+        <v>11167233.165</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B1270" t="n">
-        <v>11167233.165</v>
+        <v>17239012.79</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>17239012.79</v>
+        <v>18688241.354</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>18688241.354</v>
+        <v>22373304.463</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>22373304.463</v>
+        <v>14396933.475</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>14396933.475</v>
+        <v>14765108.135</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>14765108.135</v>
+        <v>12989124.134</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>12989124.134</v>
+        <v>10407093</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>10407093</v>
+        <v>19753403.705</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>19753403.705</v>
+        <v>8949049.268999999</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>8949049.268999999</v>
+        <v>22380338.022</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>22380338.022</v>
+        <v>12847069.898</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2024-12-29</t>
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>12847069.898</v>
+        <v>18949481.536</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>18949481.536</v>
+        <v>21888949.44</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>21888949.44</v>
+        <v>20580745.394</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>20580745.394</v>
+        <v>19403702.941</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>19403702.941</v>
+        <v>12025387.77</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B1286" t="n">
-        <v>12025387.77</v>
+        <v>11517746.211</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B1287" t="n">
-        <v>11517746.211</v>
+        <v>18648006.799</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>18648006.799</v>
+        <v>18754649.599</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>18754649.599</v>
+        <v>18605805.647</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>18605805.647</v>
+        <v>22464882.776</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>22464882.776</v>
+        <v>19098735.371</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B1292" t="n">
-        <v>19098735.371</v>
+        <v>11437944.275</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>11437944.275</v>
+        <v>15630701.474</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>15630701.474</v>
+        <v>11711443.8</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="B1295" t="n">
-        <v>11711443.8</v>
+        <v>8620307.16</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B1296" t="n">
-        <v>8620307.16</v>
+        <v>18515818.574</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>18515818.574</v>
+        <v>12856671.682</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>12856671.682</v>
+        <v>18201448.889</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="B1299" t="n">
-        <v>18201448.889</v>
+        <v>9519524.592</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>9519524.592</v>
+        <v>18421861.334</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>18421861.334</v>
+        <v>18398573.918</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>18398573.918</v>
+        <v>9308642.501</v>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>9308642.501</v>
+        <v>17331183.271</v>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>17331183.271</v>
+        <v>10333719.079</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>10333719.079</v>
+        <v>20059958.476</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>20059958.476</v>
+        <v>9481051.257999999</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>9481051.257999999</v>
+        <v>12972917.766</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>12972917.766</v>
+        <v>12827728.942</v>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>12827728.942</v>
+        <v>10843259.392</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="B1310" t="n">
-        <v>10843259.392</v>
+        <v>16829264.336</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>16829264.336</v>
+        <v>19069569.049</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2022-08-06</t>
         </is>
       </c>
       <c r="B1312" t="n">
-        <v>19069569.049</v>
+        <v>9532015.716</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B1313" t="n">
-        <v>9532015.716</v>
+        <v>17480511.655</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>17480511.655</v>
+        <v>12893419.954</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="B1315" t="n">
-        <v>12893419.954</v>
+        <v>18930025.11</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>18930025.11</v>
+        <v>13592327.934</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>13592327.934</v>
+        <v>16884075.838</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>16884075.838</v>
+        <v>8363509.02</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>8363509.02</v>
+        <v>12458643.374</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>12458643.374</v>
+        <v>11641354.93</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>11641354.93</v>
+        <v>16833334.95</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="B1322" t="n">
-        <v>16833334.95</v>
+        <v>17359924.278</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="B1323" t="n">
-        <v>17359924.278</v>
+        <v>10236215.389</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>10236215.389</v>
+        <v>8049967.714</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>8049967.714</v>
+        <v>18172193.247</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B1326" t="n">
-        <v>18172193.247</v>
+        <v>18249350.163</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B1327" t="n">
-        <v>18249350.163</v>
+        <v>19357870.444</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B1328" t="n">
-        <v>19357870.444</v>
+        <v>18829096.598</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="B1329" t="n">
-        <v>18829096.598</v>
+        <v>11410435.924</v>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="B1330" t="n">
-        <v>11410435.924</v>
+        <v>11511228.874</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="B1331" t="n">
-        <v>11511228.874</v>
+        <v>11873870.808</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B1332" t="n">
-        <v>11873870.808</v>
+        <v>16905626.816</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="B1333" t="n">
-        <v>16905626.816</v>
+        <v>9506750.107999999</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="B1334" t="n">
-        <v>9506750.107999999</v>
+        <v>10121188.898</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="B1335" t="n">
-        <v>10121188.898</v>
+        <v>15731904.375</v>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B1336" t="n">
-        <v>15731904.375</v>
+        <v>10026685.713</v>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B1337" t="n">
-        <v>10026685.713</v>
+        <v>8170042.55</v>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="B1338" t="n">
-        <v>8170042.55</v>
+        <v>6358468.879</v>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B1339" t="n">
-        <v>6358468.879</v>
+        <v>16560800.359</v>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B1340" t="n">
-        <v>16560800.359</v>
+        <v>18211536.318</v>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>18211536.318</v>
+        <v>11004721.176</v>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="B1342" t="n">
-        <v>11004721.176</v>
+        <v>11867652.532</v>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B1343" t="n">
-        <v>11867652.532</v>
+        <v>12210206.289</v>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B1344" t="n">
-        <v>12210206.289</v>
+        <v>14873483.781</v>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="B1345" t="n">
-        <v>14873483.781</v>
+        <v>8536718.226</v>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B1346" t="n">
-        <v>8536718.226</v>
+        <v>12171617.905</v>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B1347" t="n">
-        <v>12171617.905</v>
+        <v>13510242.654</v>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="B1348" t="n">
-        <v>13510242.654</v>
+        <v>19772264.652</v>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B1349" t="n">
-        <v>19772264.652</v>
+        <v>16050259.512</v>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>16050259.512</v>
+        <v>8307154.455</v>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="B1351" t="n">
-        <v>8307154.455</v>
+        <v>10451472.456</v>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>2022-11-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>10451472.456</v>
+        <v>14362928.781</v>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B1353" t="n">
-        <v>14362928.781</v>
+        <v>13491078.904</v>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B1354" t="n">
-        <v>13491078.904</v>
+        <v>20112719.639</v>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>20112719.639</v>
+        <v>20351324.136</v>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B1356" t="n">
-        <v>20351324.136</v>
+        <v>23088144.912</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B1357" t="n">
-        <v>23088144.912</v>
+        <v>14103054.216</v>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>14103054.216</v>
+        <v>19939698.057</v>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B1359" t="n">
-        <v>19939698.057</v>
+        <v>18996084.867</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="B1360" t="n">
-        <v>18996084.867</v>
+        <v>10152643.862</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B1361" t="n">
-        <v>10152643.862</v>
+        <v>9239501.051000001</v>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>9239501.051000001</v>
+        <v>10510937.957</v>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="B1363" t="n">
-        <v>10510937.957</v>
+        <v>15716836.044</v>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>15716836.044</v>
+        <v>10615483.231</v>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>2022-12-22</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B1365" t="n">
-        <v>10615483.231</v>
+        <v>15740885.312</v>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="B1366" t="n">
-        <v>15740885.312</v>
+        <v>12796519.886</v>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>12796519.886</v>
+        <v>13639848.875</v>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B1368" t="n">
-        <v>13639848.875</v>
+        <v>15795124.861</v>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B1369" t="n">
-        <v>15795124.861</v>
+        <v>22404450.46</v>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B1370" t="n">
-        <v>22404450.46</v>
+        <v>10477853.005</v>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2023-01-07</t>
         </is>
       </c>
       <c r="B1371" t="n">
-        <v>10477853.005</v>
+        <v>11376341.238</v>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>2023-01-07</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B1372" t="n">
-        <v>11376341.238</v>
+        <v>14589767.49</v>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>14589767.49</v>
+        <v>13432763.242</v>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B1374" t="n">
-        <v>13432763.242</v>
+        <v>9914365.379000001</v>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B1375" t="n">
-        <v>9914365.379000001</v>
+        <v>8871469.16</v>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B1376" t="n">
-        <v>8871469.16</v>
+        <v>8821044.728</v>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>8821044.728</v>
+        <v>11260943.27</v>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B1378" t="n">
-        <v>11260943.27</v>
+        <v>14551069.327</v>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="B1379" t="n">
-        <v>14551069.327</v>
+        <v>10360571.322</v>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B1380" t="n">
-        <v>10360571.322</v>
+        <v>8654142.73</v>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="B1381" t="n">
-        <v>8654142.73</v>
+        <v>7804497.859</v>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B1382" t="n">
-        <v>7804497.859</v>
+        <v>9388382.575999999</v>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B1383" t="n">
-        <v>9388382.575999999</v>
+        <v>9877779.377</v>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="B1384" t="n">
-        <v>9877779.377</v>
+        <v>10504922.862</v>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B1385" t="n">
-        <v>10504922.862</v>
+        <v>8660675.096000001</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B1386" t="n">
-        <v>8660675.096000001</v>
+        <v>18609730.033</v>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>18609730.033</v>
+        <v>7349744.434</v>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B1388" t="n">
-        <v>7349744.434</v>
+        <v>15643923.15</v>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B1389" t="n">
-        <v>15643923.15</v>
+        <v>18799096.649</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B1390" t="n">
-        <v>18799096.649</v>
+        <v>10857484.275</v>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="B1391" t="n">
-        <v>10857484.275</v>
+        <v>11149234.035</v>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="B1392" t="n">
-        <v>11149234.035</v>
+        <v>15621689.103</v>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="B1393" t="n">
-        <v>15621689.103</v>
+        <v>8127301.046</v>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>8127301.046</v>
+        <v>14446234.788</v>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>14446234.788</v>
+        <v>18209088.114</v>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="B1396" t="n">
-        <v>18209088.114</v>
+        <v>10805935.58</v>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B1397" t="n">
-        <v>10805935.58</v>
+        <v>22365594.535</v>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>22365594.535</v>
+        <v>8486747.433</v>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>8486747.433</v>
+        <v>14010038.153</v>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>14010038.153</v>
+        <v>12870879.477</v>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B1401" t="n">
-        <v>12870879.477</v>
+        <v>15346852.871</v>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B1402" t="n">
-        <v>15346852.871</v>
+        <v>9114476.312000001</v>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="B1403" t="n">
-        <v>9114476.312000001</v>
+        <v>10847808.277</v>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B1404" t="n">
-        <v>10847808.277</v>
+        <v>8877780.388</v>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>8877780.388</v>
+        <v>22259727.582</v>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>22259727.582</v>
+        <v>17968690.541</v>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="B1407" t="n">
-        <v>17968690.541</v>
+        <v>8346328.634</v>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="B1408" t="n">
-        <v>8346328.634</v>
+        <v>18882222.042</v>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>18882222.042</v>
+        <v>9386582.370999999</v>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B1410" t="n">
-        <v>9386582.370999999</v>
+        <v>10773183.386</v>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>10773183.386</v>
+        <v>16585261.576</v>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="B1412" t="n">
-        <v>16585261.576</v>
+        <v>16236706.926</v>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B1413" t="n">
-        <v>16236706.926</v>
+        <v>21808754.591</v>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B1414" t="n">
-        <v>21808754.591</v>
+        <v>20554065.145</v>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="B1415" t="n">
-        <v>20554065.145</v>
+        <v>7902657.124</v>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B1416" t="n">
-        <v>7902657.124</v>
+        <v>14252744.065</v>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B1417" t="n">
-        <v>14252744.065</v>
+        <v>10658742.561</v>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B1418" t="n">
-        <v>10658742.561</v>
+        <v>18727823.649</v>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B1419" t="n">
-        <v>18727823.649</v>
+        <v>10503343.65</v>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B1420" t="n">
-        <v>10503343.65</v>
+        <v>10785349.848</v>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B1421" t="n">
-        <v>10785349.848</v>
+        <v>18803774.412</v>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B1422" t="n">
-        <v>18803774.412</v>
+        <v>18746833.543</v>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B1423" t="n">
-        <v>18746833.543</v>
+        <v>14696488.122</v>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B1424" t="n">
-        <v>14696488.122</v>
+        <v>13074131.781</v>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="B1425" t="n">
-        <v>13074131.781</v>
+        <v>11136369.663</v>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B1426" t="n">
-        <v>11136369.663</v>
+        <v>22620694.513</v>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>22620694.513</v>
+        <v>19760413.223</v>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="B1428" t="n">
-        <v>19760413.223</v>
+        <v>11420107.846</v>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B1429" t="n">
-        <v>11420107.846</v>
+        <v>12841467.318</v>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B1430" t="n">
-        <v>12841467.318</v>
+        <v>19272529.034</v>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B1431" t="n">
-        <v>19272529.034</v>
+        <v>11384746.006</v>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B1432" t="n">
-        <v>11384746.006</v>
+        <v>19496972.836</v>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>19496972.836</v>
+        <v>12225489.867</v>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="B1434" t="n">
-        <v>12225489.867</v>
+        <v>11477197.525</v>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B1435" t="n">
-        <v>11477197.525</v>
+        <v>11313913.816</v>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B1436" t="n">
-        <v>11313913.816</v>
+        <v>18346710.052</v>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B1437" t="n">
-        <v>18346710.052</v>
+        <v>18616838.388</v>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B1438" t="n">
-        <v>18616838.388</v>
+        <v>16688077.13</v>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B1439" t="n">
-        <v>16688077.13</v>
+        <v>19740398.471</v>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="B1440" t="n">
-        <v>19740398.471</v>
+        <v>8386250.008</v>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B1441" t="n">
-        <v>8386250.008</v>
+        <v>15303734.889</v>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>15303734.889</v>
+        <v>11978202.448</v>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B1443" t="n">
-        <v>11978202.448</v>
+        <v>16127948.086</v>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>16127948.086</v>
+        <v>19006487.04</v>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>19006487.04</v>
+        <v>17569350.656</v>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>17569350.656</v>
+        <v>17249482.25</v>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B1447" t="n">
-        <v>17249482.25</v>
+        <v>17225229.436</v>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B1448" t="n">
-        <v>17225229.436</v>
+        <v>17153769.299</v>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>17153769.299</v>
+        <v>17115867.282</v>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>17115867.282</v>
+        <v>17049245.734</v>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>17049245.734</v>
+        <v>16833063.951</v>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>16833063.951</v>
+        <v>16784620.262</v>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>16784620.262</v>
+        <v>12895454.923</v>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B1454" t="n">
-        <v>12895454.923</v>
+        <v>11691372.317</v>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>11691372.317</v>
-      </c>
-    </row>
-    <row r="1456">
-      <c r="A1456" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="B1456" t="n">
         <v>16110702.506</v>
       </c>
     </row>

--- a/data_cripto/btc_cdd.xlsx
+++ b/data_cripto/btc_cdd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1455"/>
+  <dimension ref="A1:B1462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8241,6740 +8241,6796 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
-        </is>
-      </c>
-      <c r="B782" t="n">
-        <v>13341241.993</v>
-      </c>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="B783" t="n">
-        <v>6157939.79</v>
+        <v>13341241.993</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="B784" t="n">
-        <v>19491754.348</v>
+        <v>6157939.79</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B785" t="n">
-        <v>19364978.541</v>
+        <v>19491754.348</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B786" t="n">
-        <v>13081600.613</v>
+        <v>19364978.541</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B787" t="n">
-        <v>18544156.315</v>
+        <v>13081600.613</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B788" t="n">
-        <v>22781633.493</v>
+        <v>18544156.315</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B789" t="n">
-        <v>20134091.782</v>
+        <v>22781633.493</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B790" t="n">
-        <v>11558581.84</v>
+        <v>20134091.782</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="B791" t="n">
-        <v>12537010.834</v>
+        <v>11558581.84</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="B792" t="n">
-        <v>20373760.584</v>
+        <v>12537010.834</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B793" t="n">
-        <v>10484383.589</v>
+        <v>20373760.584</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="B794" t="n">
-        <v>9998998.189999999</v>
+        <v>10484383.589</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B795" t="n">
-        <v>22737857.951</v>
+        <v>9998998.189999999</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B796" t="n">
-        <v>18622231.291</v>
+        <v>22737857.951</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B797" t="n">
-        <v>20073001.694</v>
-      </c>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B798" t="n">
-        <v>12479784.143</v>
+        <v>18622231.291</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2023-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B799" t="n">
-        <v>11202219.813</v>
+        <v>20073001.694</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B800" t="n">
-        <v>19488856.888</v>
-      </c>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B801" t="n">
-        <v>20290260.414</v>
+        <v>12479784.143</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2023-01-21</t>
         </is>
       </c>
       <c r="B802" t="n">
-        <v>9164060.566</v>
+        <v>11202219.813</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B803" t="n">
-        <v>9978731.368000001</v>
+        <v>19488856.888</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B804" t="n">
-        <v>19276662.685</v>
+        <v>20290260.414</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B805" t="n">
-        <v>22731990.232</v>
+        <v>9164060.566</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2024-01-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B806" t="n">
-        <v>11542678.001</v>
+        <v>9978731.368000001</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B807" t="n">
-        <v>11113889.507</v>
+        <v>19276662.685</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="B808" t="n">
-        <v>17369284.699</v>
-      </c>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B809" t="n">
-        <v>18704073.361</v>
+        <v>22731990.232</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-01-21</t>
         </is>
       </c>
       <c r="B810" t="n">
-        <v>12896927.965</v>
+        <v>11542678.001</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="B811" t="n">
-        <v>15094527.378</v>
+        <v>11113889.507</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B812" t="n">
-        <v>19189656.128</v>
+        <v>17369284.699</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="B813" t="n">
-        <v>18302045.464</v>
+        <v>18704073.361</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B814" t="n">
-        <v>11659256.274</v>
+        <v>12896927.965</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="B815" t="n">
-        <v>7099585.826</v>
+        <v>15094527.378</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B816" t="n">
-        <v>18651305.009</v>
+        <v>19189656.128</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="B817" t="n">
-        <v>12621325.666</v>
-      </c>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B818" t="n">
-        <v>18241859.779</v>
+        <v>18302045.464</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2024-01-20</t>
         </is>
       </c>
       <c r="B819" t="n">
-        <v>18371824.607</v>
+        <v>11659256.274</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="B820" t="n">
-        <v>12613297.678</v>
+        <v>7099585.826</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="B821" t="n">
-        <v>9009907.584000001</v>
+        <v>18651305.009</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="B822" t="n">
-        <v>7262346.794</v>
+        <v>12621325.666</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="B823" t="n">
-        <v>11790940.288</v>
-      </c>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B824" t="n">
-        <v>14241963.788</v>
+        <v>18241859.779</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B825" t="n">
-        <v>9314280.655999999</v>
+        <v>18371824.607</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B826" t="n">
-        <v>8435586.448999999</v>
+        <v>12613297.678</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="B827" t="n">
-        <v>18201441.188</v>
+        <v>9009907.584000001</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="B828" t="n">
-        <v>18538635.409</v>
+        <v>7262346.794</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="B829" t="n">
-        <v>11679256.547</v>
+        <v>11790940.288</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B830" t="n">
-        <v>19083050.476</v>
+        <v>14241963.788</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B831" t="n">
-        <v>9764053.578</v>
+        <v>9314280.655999999</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B832" t="n">
-        <v>10099290.923</v>
+        <v>8435586.448999999</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="B833" t="n">
-        <v>7424642.418</v>
-      </c>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B834" t="n">
-        <v>7857027.699</v>
+        <v>18201441.188</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="B835" t="n">
-        <v>16631884.627</v>
+        <v>18538635.409</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="B836" t="n">
-        <v>16239638.189</v>
+        <v>11679256.547</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B837" t="n">
-        <v>10256549.609</v>
+        <v>19083050.476</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="B838" t="n">
-        <v>8399036.956</v>
+        <v>9764053.578</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="B839" t="n">
-        <v>7385502.356</v>
+        <v>10099290.923</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>2023-04-09</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="B840" t="n">
-        <v>7790771.387</v>
+        <v>7424642.418</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="B841" t="n">
-        <v>16247365.076</v>
+        <v>7857027.699</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B842" t="n">
-        <v>15736142.041</v>
+        <v>16631884.627</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B843" t="n">
-        <v>11582238.375</v>
+        <v>16239638.189</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B844" t="n">
-        <v>17100619.249</v>
+        <v>10256549.609</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B845" t="n">
-        <v>18589231.384</v>
+        <v>8399036.956</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="B846" t="n">
-        <v>10874670.685</v>
+        <v>7385502.356</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="B847" t="n">
-        <v>17174758.833</v>
+        <v>7790771.387</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B848" t="n">
-        <v>8248305.772</v>
+        <v>16247365.076</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B849" t="n">
-        <v>7101135.828</v>
+        <v>15736142.041</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B850" t="n">
-        <v>7738526.17</v>
+        <v>11582238.375</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="B851" t="n">
-        <v>15761228.259</v>
+        <v>17100619.249</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B852" t="n">
-        <v>14643596.316</v>
+        <v>18589231.384</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B853" t="n">
-        <v>14953650.236</v>
+        <v>10874670.685</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B854" t="n">
-        <v>19797080.874</v>
+        <v>17174758.833</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B855" t="n">
-        <v>12764248.542</v>
+        <v>8248305.772</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="B856" t="n">
-        <v>22635699.612</v>
+        <v>7101135.828</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="B857" t="n">
-        <v>13907293</v>
+        <v>7738526.17</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B858" t="n">
-        <v>12970976.352</v>
+        <v>15761228.259</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B859" t="n">
-        <v>12127249.673</v>
+        <v>14643596.316</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B860" t="n">
-        <v>18471889.87</v>
+        <v>14953650.236</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B861" t="n">
-        <v>6896044.41</v>
+        <v>19797080.874</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B862" t="n">
-        <v>8439099.912</v>
+        <v>12764248.542</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B863" t="n">
-        <v>7755708.176</v>
+        <v>22635699.612</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B864" t="n">
-        <v>7308899.176</v>
+        <v>13907293</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B865" t="n">
-        <v>9621408.710999999</v>
+        <v>12970976.352</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B866" t="n">
-        <v>6462474.853</v>
+        <v>12127249.673</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B867" t="n">
-        <v>8566983.523</v>
+        <v>18471889.87</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="B868" t="n">
-        <v>20098428.408</v>
+        <v>6896044.41</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="B869" t="n">
-        <v>15606452.27</v>
+        <v>8439099.912</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="B870" t="n">
-        <v>14412675.915</v>
+        <v>7755708.176</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="B871" t="n">
-        <v>13956296.548</v>
+        <v>7308899.176</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B872" t="n">
-        <v>14629813.48</v>
+        <v>9621408.710999999</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="B873" t="n">
-        <v>19643216.711</v>
+        <v>6462474.853</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="B874" t="n">
-        <v>17924810.11</v>
+        <v>8566983.523</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B875" t="n">
-        <v>13027523.41</v>
+        <v>20098428.408</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B876" t="n">
-        <v>11767425.853</v>
+        <v>15606452.27</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B877" t="n">
-        <v>11175600.083</v>
+        <v>14412675.915</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B878" t="n">
-        <v>18712982.753</v>
+        <v>13956296.548</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B879" t="n">
-        <v>22302001.616</v>
+        <v>14629813.48</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="B880" t="n">
-        <v>14537522.035</v>
+        <v>19643216.711</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B881" t="n">
-        <v>6727091.183</v>
+        <v>17924810.11</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B882" t="n">
-        <v>8555289.42</v>
+        <v>13027523.41</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B883" t="n">
-        <v>19068613.398</v>
+        <v>11767425.853</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B884" t="n">
-        <v>19607541.091</v>
+        <v>11175600.083</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B885" t="n">
-        <v>11773781.574</v>
+        <v>18712982.753</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B886" t="n">
-        <v>11472533.708</v>
+        <v>22302001.616</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B887" t="n">
-        <v>10960901.755</v>
+        <v>14537522.035</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="B888" t="n">
-        <v>6334883.839</v>
+        <v>6727091.183</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="B889" t="n">
-        <v>8428845.960000001</v>
+        <v>8555289.42</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B890" t="n">
-        <v>7198424.409</v>
+        <v>19068613.398</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B891" t="n">
-        <v>6363611.213</v>
+        <v>19607541.091</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="B892" t="n">
-        <v>22293668.179</v>
+        <v>11773781.574</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B893" t="n">
-        <v>18802206.57</v>
+        <v>11472533.708</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B894" t="n">
-        <v>19533875.913</v>
+        <v>10960901.755</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="B895" t="n">
-        <v>11236310.555</v>
+        <v>6334883.839</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="B896" t="n">
-        <v>8780639.027000001</v>
+        <v>8428845.960000001</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="B897" t="n">
-        <v>8765170.851</v>
+        <v>7198424.409</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="B898" t="n">
-        <v>6341030.98</v>
+        <v>6363611.213</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B899" t="n">
-        <v>8732498.423</v>
+        <v>22293668.179</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B900" t="n">
-        <v>15591768.587</v>
+        <v>18802206.57</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B901" t="n">
-        <v>19428788.229</v>
+        <v>19533875.913</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="B902" t="n">
-        <v>12905243.969</v>
+        <v>11236310.555</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B903" t="n">
-        <v>11104124.122</v>
+        <v>8780639.027000001</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B904" t="n">
-        <v>16292961.358</v>
+        <v>8765170.851</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="B905" t="n">
-        <v>17534010.522</v>
+        <v>6341030.98</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="B906" t="n">
-        <v>8593046.018999999</v>
+        <v>8732498.423</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B907" t="n">
-        <v>8643707.628</v>
+        <v>15591768.587</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B908" t="n">
-        <v>8469308.615</v>
+        <v>19428788.229</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B909" t="n">
-        <v>13998155.439</v>
+        <v>12905243.969</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B910" t="n">
-        <v>7557511.107</v>
+        <v>11104124.122</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B911" t="n">
-        <v>7631521.423</v>
+        <v>16292961.358</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B912" t="n">
-        <v>14270593.852</v>
+        <v>17534010.522</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B913" t="n">
-        <v>12852439.253</v>
+        <v>8593046.018999999</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B914" t="n">
-        <v>19841169.248</v>
+        <v>8643707.628</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B915" t="n">
-        <v>17561246.532</v>
+        <v>8469308.615</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B916" t="n">
-        <v>22737795.907</v>
+        <v>13998155.439</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="B917" t="n">
-        <v>7259411.135</v>
+        <v>7557511.107</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="B918" t="n">
-        <v>7667763.401</v>
+        <v>7631521.423</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B919" t="n">
-        <v>14785600.127</v>
+        <v>14270593.852</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B920" t="n">
-        <v>18527947.46</v>
+        <v>12852439.253</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B921" t="n">
-        <v>12722932.507</v>
+        <v>19841169.248</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="B922" t="n">
-        <v>11938735.729</v>
+        <v>17561246.532</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B923" t="n">
-        <v>9456428.016000001</v>
+        <v>22737795.907</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="B924" t="n">
-        <v>21605324.815</v>
+        <v>7259411.135</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="B925" t="n">
-        <v>18492433.512</v>
+        <v>7667763.401</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B926" t="n">
-        <v>22439055.215</v>
+        <v>14785600.127</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B927" t="n">
-        <v>13825417.492</v>
+        <v>18527947.46</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B928" t="n">
-        <v>12729614.685</v>
+        <v>12722932.507</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B929" t="n">
-        <v>9736790.387</v>
+        <v>11938735.729</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B930" t="n">
-        <v>6587399.075</v>
+        <v>9456428.016000001</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B931" t="n">
-        <v>8774103.695</v>
+        <v>21605324.815</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B932" t="n">
-        <v>7299061.636</v>
+        <v>18492433.512</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B933" t="n">
-        <v>7108260.131</v>
+        <v>22439055.215</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>2023-03-11</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B934" t="n">
-        <v>7126453.134</v>
+        <v>13825417.492</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B935" t="n">
-        <v>9809232.718</v>
+        <v>12729614.685</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B936" t="n">
-        <v>9507766.615</v>
+        <v>9736790.387</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="B937" t="n">
-        <v>6592549.217</v>
+        <v>6587399.075</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="B938" t="n">
-        <v>8080528.574</v>
+        <v>8774103.695</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="B939" t="n">
-        <v>7095491.394</v>
+        <v>7299061.636</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="B940" t="n">
-        <v>12673319.268</v>
+        <v>7108260.131</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2023-03-11</t>
         </is>
       </c>
       <c r="B941" t="n">
-        <v>10793064.387</v>
+        <v>7126453.134</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="B942" t="n">
-        <v>16727091.234</v>
+        <v>9809232.718</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="B943" t="n">
-        <v>9180043.688999999</v>
+        <v>9507766.615</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="B944" t="n">
-        <v>22432909.296</v>
+        <v>6592549.217</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="B945" t="n">
-        <v>17616871.188</v>
+        <v>8080528.574</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="B946" t="n">
-        <v>6872584.918</v>
+        <v>7095491.394</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B947" t="n">
-        <v>8176718.612</v>
+        <v>12673319.268</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B948" t="n">
-        <v>7455548.867</v>
+        <v>10793064.387</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B949" t="n">
-        <v>18459379.883</v>
+        <v>16727091.234</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B950" t="n">
-        <v>17791123.577</v>
+        <v>9180043.688999999</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B951" t="n">
-        <v>18932006.014</v>
+        <v>22432909.296</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B952" t="n">
-        <v>13312479.096</v>
+        <v>17616871.188</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="B953" t="n">
-        <v>22087864.099</v>
+        <v>6872584.918</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="B954" t="n">
-        <v>20597824.491</v>
+        <v>8176718.612</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="B955" t="n">
-        <v>7083228.662</v>
+        <v>7455548.867</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B956" t="n">
-        <v>8262471.2</v>
+        <v>18459379.883</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B957" t="n">
-        <v>8373661.789</v>
+        <v>17791123.577</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>2022-07-23</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B958" t="n">
-        <v>9903067.517999999</v>
+        <v>18932006.014</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B959" t="n">
-        <v>18126267.628</v>
+        <v>13312479.096</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B960" t="n">
-        <v>11310855.322</v>
+        <v>22087864.099</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B961" t="n">
-        <v>16732457.517</v>
+        <v>20597824.491</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="B962" t="n">
-        <v>17541534.802</v>
+        <v>7083228.662</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="B963" t="n">
-        <v>10071130.987</v>
+        <v>8262471.2</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="B964" t="n">
-        <v>22411126.263</v>
+        <v>8373661.789</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2022-07-23</t>
         </is>
       </c>
       <c r="B965" t="n">
-        <v>22654358.577</v>
+        <v>9903067.517999999</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B966" t="n">
-        <v>8445638.851</v>
+        <v>18126267.628</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B967" t="n">
-        <v>7977963.589</v>
+        <v>11310855.322</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B968" t="n">
-        <v>8042090.576</v>
+        <v>16732457.517</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B969" t="n">
-        <v>18601572.678</v>
+        <v>17541534.802</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B970" t="n">
-        <v>18902714.615</v>
+        <v>10071130.987</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B971" t="n">
-        <v>19176092.195</v>
+        <v>22411126.263</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="B972" t="n">
-        <v>18263481.818</v>
+        <v>22654358.577</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="B973" t="n">
-        <v>11393282.759</v>
+        <v>8445638.851</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2023-07-16</t>
         </is>
       </c>
       <c r="B974" t="n">
-        <v>12057555.671</v>
+        <v>7977963.589</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="B975" t="n">
-        <v>16504964.214</v>
+        <v>8042090.576</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B976" t="n">
-        <v>10155336.497</v>
+        <v>18601572.678</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B977" t="n">
-        <v>15737013.492</v>
+        <v>18902714.615</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B978" t="n">
-        <v>8768767.397</v>
+        <v>19176092.195</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B979" t="n">
-        <v>10334944.759</v>
+        <v>18263481.818</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B980" t="n">
-        <v>7978148.013</v>
+        <v>11393282.759</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B981" t="n">
-        <v>8121738.785</v>
+        <v>12057555.671</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B982" t="n">
-        <v>18009208.082</v>
+        <v>16504964.214</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B983" t="n">
-        <v>13706271.631</v>
+        <v>10155336.497</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B984" t="n">
-        <v>11743400.645</v>
+        <v>15737013.492</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="B985" t="n">
-        <v>12602780.311</v>
+        <v>8768767.397</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B986" t="n">
-        <v>22539237.596</v>
+        <v>10334944.759</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="B987" t="n">
-        <v>10260081.547</v>
+        <v>7978148.013</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="B988" t="n">
-        <v>8025625.18</v>
+        <v>8121738.785</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B989" t="n">
-        <v>7675150.205</v>
+        <v>18009208.082</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B990" t="n">
-        <v>22724057.329</v>
+        <v>13706271.631</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B991" t="n">
-        <v>13373154.572</v>
+        <v>11743400.645</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="B992" t="n">
-        <v>14153820.75</v>
+        <v>12602780.311</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B993" t="n">
-        <v>19778813.536</v>
+        <v>22539237.596</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="B994" t="n">
-        <v>15807832.072</v>
+        <v>10260081.547</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="B995" t="n">
-        <v>15054523.106</v>
+        <v>8025625.18</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="B996" t="n">
-        <v>12254468.78</v>
+        <v>7675150.205</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B997" t="n">
-        <v>8847168.232000001</v>
+        <v>22724057.329</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="B998" t="n">
-        <v>7658732.99</v>
+        <v>13373154.572</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B999" t="n">
-        <v>11222124.303</v>
+        <v>14153820.75</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>18425206.647</v>
+        <v>19778813.536</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>20304151.013</v>
+        <v>15807832.072</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>13043079.95</v>
+        <v>15054523.106</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>8404561.468</v>
+        <v>12254468.78</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>2023-03-06</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>6922295.32</v>
+        <v>8847168.232000001</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>20059418.345</v>
+        <v>7658732.99</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>19888945.755</v>
+        <v>11222124.303</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>10079264.693</v>
+        <v>18425206.647</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>15732205.442</v>
+        <v>20304151.013</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>16254770.186</v>
+        <v>13043079.95</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>7982545.503</v>
+        <v>8404561.468</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>10906294.323</v>
+        <v>6922295.32</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>19168386.018</v>
+        <v>20059418.345</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>12991619.239</v>
+        <v>19888945.755</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>15736124.913</v>
+        <v>10079264.693</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>16404541.597</v>
+        <v>15732205.442</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>7795415.295</v>
+        <v>16254770.186</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>7199162.719</v>
+        <v>7982545.503</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2023-01-25</t>
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>11049519.078</v>
+        <v>10906294.323</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>13180955.134</v>
+        <v>19168386.018</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>19840596.87</v>
+        <v>12991619.239</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>7370614.503</v>
+        <v>15736124.913</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>11003994.747</v>
+        <v>16404541.597</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>19817395.793</v>
+        <v>7795415.295</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>6847142.251</v>
+        <v>7199162.719</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>10726120.682</v>
+        <v>11049519.078</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>18020855.515</v>
+        <v>13180955.134</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>20400661.749</v>
+        <v>19840596.87</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>9193966.23</v>
+        <v>7370614.503</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>9875068.106000001</v>
+        <v>11003994.747</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>8240253.28</v>
+        <v>19817395.793</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>10216742.553</v>
+        <v>6847142.251</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2022-12-28</t>
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>18534074.954</v>
+        <v>10726120.682</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>6352507.324</v>
+        <v>18020855.515</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>10390293.772</v>
+        <v>20400661.749</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>16267909.581</v>
+        <v>9193966.23</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>11123186.066</v>
+        <v>9875068.106000001</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>15459847.995</v>
+        <v>8240253.28</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>17208008.89</v>
+        <v>10216742.553</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>6605806.716</v>
+        <v>18534074.954</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>2023-03-12</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>7103905.636</v>
+        <v>6352507.324</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
+          <t>2022-12-08</t>
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>9512207.699999999</v>
+        <v>10390293.772</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>2022-12-09</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>10466814.972</v>
+        <v>16267909.581</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>2022-11-27</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>10201894.128</v>
+        <v>11123186.066</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>6008052.168</v>
+        <v>15459847.995</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>9027679.793</v>
+        <v>17208008.89</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>8296788.778</v>
+        <v>6605806.716</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2023-03-12</t>
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>14504226.874</v>
+        <v>7103905.636</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>18389579.978</v>
+        <v>9512207.699999999</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-12-09</t>
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>8134887.795</v>
+        <v>10466814.972</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2022-11-27</t>
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>21647135.032</v>
+        <v>10201894.128</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>6311486.07</v>
+        <v>6008052.168</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-05-31</t>
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>6145982.891</v>
+        <v>9027679.793</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>14713290.066</v>
+        <v>8296788.778</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>12633844.31</v>
+        <v>14504226.874</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>14392379.583</v>
+        <v>18389579.978</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>9270561.718</v>
+        <v>8134887.795</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>22718316.548</v>
+        <v>21647135.032</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>15763556.203</v>
+        <v>6311486.07</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>13991670.579</v>
+        <v>6145982.891</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>18263584.952</v>
+        <v>14713290.066</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>19066275.837</v>
+        <v>12633844.31</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>9314345.433</v>
+        <v>14392379.583</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>9533111.244000001</v>
+        <v>9270561.718</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>17664296.466</v>
+        <v>22718316.548</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>6817299.489</v>
+        <v>15763556.203</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>6115150.616</v>
+        <v>13991670.579</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>10134422.693</v>
+        <v>18263584.952</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>16703777.294</v>
+        <v>19066275.837</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>16241686.46</v>
+        <v>9314345.433</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>7028591.115</v>
+        <v>9533111.244000001</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>5811075.696</v>
+        <v>17664296.466</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>15637289.008</v>
+        <v>6817299.489</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>11414106.357</v>
+        <v>6115150.616</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>18706071.644</v>
+        <v>10134422.693</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>10942825.102</v>
+        <v>16703777.294</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>17268706.198</v>
+        <v>16241686.46</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>17197990.83</v>
+        <v>7028591.115</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>22239298.739</v>
+        <v>5811075.696</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>10855068.422</v>
+        <v>15637289.008</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>7255143.779</v>
+        <v>11414106.357</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>7812804.752</v>
+        <v>18706071.644</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>14208722.448</v>
+        <v>10942825.102</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>14616694.16</v>
+        <v>17268706.198</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>14737879.389</v>
+        <v>17197990.83</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>12933809.709</v>
+        <v>22239298.739</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>8805171.127</v>
+        <v>10855068.422</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>7308221.44</v>
+        <v>7255143.779</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>7888570.236</v>
+        <v>7812804.752</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>14547539.62</v>
+        <v>14208722.448</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>19746507.73</v>
+        <v>14616694.16</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>8711949.614</v>
+        <v>14737879.389</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>8660832.931</v>
+        <v>12933809.709</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>11885242.465</v>
+        <v>8805171.127</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>7876220.229</v>
+        <v>7308221.44</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>9153056.618000001</v>
+        <v>7888570.236</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>14270964.112</v>
+        <v>14547539.62</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>12988051.483</v>
+        <v>19746507.73</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>11292858.688</v>
+        <v>8711949.614</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>18760597.04</v>
+        <v>8660832.931</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>8515955.833000001</v>
+        <v>11885242.465</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>21596321.606</v>
+        <v>7876220.229</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>8473097.453</v>
+        <v>9153056.618000001</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>18630467.666</v>
+        <v>14270964.112</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>14806048.067</v>
+        <v>12988051.483</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>18567759.562</v>
+        <v>11292858.688</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>19476737.258</v>
+        <v>18760597.04</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>11785461.662</v>
+        <v>8515955.833000001</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>11513696.526</v>
+        <v>21596321.606</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>18612923.858</v>
+        <v>8473097.453</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>11371015.617</v>
+        <v>18630467.666</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>22204696.845</v>
+        <v>14806048.067</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>8551266.077</v>
+        <v>18567759.562</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>18785986.856</v>
+        <v>19476737.258</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>16660029.347</v>
+        <v>11785461.662</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>9524420.506999999</v>
+        <v>11513696.526</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>11377694.684</v>
+        <v>18612923.858</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>16169923.625</v>
+        <v>11371015.617</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>11482296.535</v>
+        <v>22204696.845</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="B1119" t="n">
-        <v>17132879.503</v>
+        <v>8551266.077</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>9114024.970000001</v>
+        <v>18785986.856</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>22408841.94</v>
+        <v>16660029.347</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="B1122" t="n">
-        <v>18000654.264</v>
+        <v>9524420.506999999</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>10359819.603</v>
+        <v>11377694.684</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>18496989.062</v>
+        <v>16169923.625</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>12884767.419</v>
+        <v>11482296.535</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B1126" t="n">
-        <v>17551353.824</v>
+        <v>17132879.503</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B1127" t="n">
-        <v>22027054.945</v>
+        <v>9114024.970000001</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>20584053.911</v>
+        <v>22408841.94</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>17263752.185</v>
+        <v>18000654.264</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="B1130" t="n">
-        <v>10277655.606</v>
+        <v>10359819.603</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B1131" t="n">
-        <v>6598014.235</v>
+        <v>18496989.062</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="B1132" t="n">
-        <v>13906083.942</v>
+        <v>12884767.419</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>18768996.357</v>
+        <v>17551353.824</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>11670457.865</v>
+        <v>22027054.945</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B1135" t="n">
-        <v>18523673.383</v>
+        <v>20584053.911</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>18983749.017</v>
+        <v>17263752.185</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B1137" t="n">
-        <v>10054424.048</v>
+        <v>10277655.606</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>22607441.191</v>
+        <v>6598014.235</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>2022-12-02</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>10435634.731</v>
+        <v>13906083.942</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B1140" t="n">
-        <v>9212749.865</v>
+        <v>18768996.357</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B1141" t="n">
-        <v>7702956.401</v>
+        <v>11670457.865</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>7280535.923</v>
+        <v>18523673.383</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B1143" t="n">
-        <v>7953269.825</v>
+        <v>18983749.017</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B1144" t="n">
-        <v>12216862.024</v>
+        <v>10054424.048</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>8017070.673</v>
+        <v>22607441.191</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>2023-02-17</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="B1146" t="n">
-        <v>8112862.961</v>
+        <v>10435634.731</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>8173999.195</v>
+        <v>9212749.865</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="B1148" t="n">
-        <v>9524273.433</v>
+        <v>7702956.401</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>10213288.827</v>
+        <v>7280535.923</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>10273334.73</v>
+        <v>7953269.825</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>14044333.608</v>
+        <v>12216862.024</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>22565977.841</v>
+        <v>8017070.673</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-02-17</t>
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>12620748.822</v>
+        <v>8112862.961</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>10786270.903</v>
+        <v>8173999.195</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>19809679.403</v>
+        <v>9524273.433</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>8214760.012</v>
+        <v>10213288.827</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>8200427.591</v>
+        <v>10273334.73</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>8261999.766</v>
+        <v>14044333.608</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>7760533.554</v>
+        <v>22565977.841</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B1160" t="n">
-        <v>10366318.076</v>
+        <v>12620748.822</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B1161" t="n">
-        <v>9030081.539999999</v>
+        <v>10786270.903</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>2022-11-26</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>10362802.579</v>
+        <v>19809679.403</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>6153661.361</v>
+        <v>8214760.012</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="B1164" t="n">
-        <v>6190194.949</v>
+        <v>8200427.591</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="B1165" t="n">
-        <v>9874969.986</v>
+        <v>8261999.766</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="B1166" t="n">
-        <v>9880601.411</v>
+        <v>7760533.554</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>16777254.692</v>
+        <v>10366318.076</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>12798520.113</v>
+        <v>9030081.539999999</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2022-11-26</t>
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>12614002.689</v>
+        <v>10362802.579</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>17508953.532</v>
+        <v>6153661.361</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>18944691.526</v>
+        <v>6190194.949</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="B1172" t="n">
-        <v>13539397.76</v>
+        <v>9874969.986</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>16908871.181</v>
+        <v>9880601.411</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>8145459.209</v>
+        <v>16777254.692</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>12536685.09</v>
+        <v>12798520.113</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>11570457.865</v>
+        <v>12614002.689</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>11463487.194</v>
+        <v>17508953.532</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>16742051.234</v>
+        <v>18944691.526</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="B1179" t="n">
-        <v>17420607.699</v>
+        <v>13539397.76</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>10154290.861</v>
+        <v>16908871.181</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>18283375.171</v>
+        <v>8145459.209</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>20197508.371</v>
+        <v>12536685.09</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>13198740.126</v>
+        <v>11570457.865</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>7391634.265</v>
+        <v>11463487.194</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B1185" t="n">
-        <v>19324380.182</v>
+        <v>16742051.234</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B1186" t="n">
-        <v>18518628.999</v>
+        <v>17420607.699</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B1187" t="n">
-        <v>11533542.22</v>
+        <v>10154290.861</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B1188" t="n">
-        <v>11982419.652</v>
+        <v>18283375.171</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B1189" t="n">
-        <v>16662741.532</v>
+        <v>20197508.371</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>10165678.695</v>
+        <v>13198740.126</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="B1191" t="n">
-        <v>15762243.002</v>
+        <v>7391634.265</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>13742960</v>
+        <v>19324380.182</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B1193" t="n">
-        <v>6889732.972</v>
+        <v>18518628.999</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>17921349.452</v>
+        <v>11533542.22</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>11890718.505</v>
+        <v>11982419.652</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B1196" t="n">
-        <v>12190152.036</v>
+        <v>16662741.532</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="B1197" t="n">
-        <v>19240581.039</v>
+        <v>10165678.695</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>15843658.658</v>
+        <v>15762243.002</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B1199" t="n">
-        <v>7680678.394</v>
+        <v>13742960</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>13422882.236</v>
+        <v>6889732.972</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B1201" t="n">
-        <v>13888250.184</v>
+        <v>17921349.452</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B1202" t="n">
-        <v>19799814.996</v>
+        <v>11890718.505</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>16092268.729</v>
+        <v>12190152.036</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B1204" t="n">
-        <v>19077349.963</v>
+        <v>19240581.039</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>2023-03-27</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B1205" t="n">
-        <v>7424064.951</v>
+        <v>15843658.658</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="B1206" t="n">
-        <v>13449347.64</v>
+        <v>7680678.394</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="B1207" t="n">
-        <v>19554838.811</v>
+        <v>13422882.236</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>2023-01-08</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B1208" t="n">
-        <v>11379536.421</v>
+        <v>13888250.184</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="B1209" t="n">
-        <v>18061928.338</v>
+        <v>19799814.996</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B1210" t="n">
-        <v>18195056.999</v>
+        <v>16092268.729</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="B1211" t="n">
-        <v>20311437.78</v>
+        <v>19077349.963</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="B1212" t="n">
-        <v>19921671.37</v>
+        <v>7424064.951</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B1213" t="n">
-        <v>10139727.84</v>
+        <v>13449347.64</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>15736728.197</v>
+        <v>19554838.811</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2023-01-08</t>
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>8237636.144</v>
+        <v>11379536.421</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>10034680.589</v>
+        <v>18061928.338</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>19912305.448</v>
+        <v>18195056.999</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>11252026.475</v>
+        <v>20311437.78</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B1219" t="n">
-        <v>16368609.325</v>
+        <v>19921671.37</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>13010963.419</v>
+        <v>10139727.84</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>15408192.117</v>
+        <v>15736728.197</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>17931313.804</v>
+        <v>8237636.144</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>10313035.77</v>
+        <v>10034680.589</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>13202621.428</v>
+        <v>19912305.448</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2023-01-05</t>
         </is>
       </c>
       <c r="B1225" t="n">
-        <v>8301700.833</v>
+        <v>11252026.475</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>17680988.152</v>
+        <v>16368609.325</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="B1227" t="n">
-        <v>7860090.304</v>
+        <v>13010963.419</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>14555529.314</v>
+        <v>15408192.117</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B1229" t="n">
-        <v>9250585.187000001</v>
+        <v>17931313.804</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>17316630.871</v>
+        <v>10313035.77</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>9643468.957</v>
+        <v>13202621.428</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>22762705.257</v>
+        <v>8301700.833</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B1233" t="n">
-        <v>15903527.022</v>
+        <v>17680988.152</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="B1234" t="n">
-        <v>14080491.729</v>
+        <v>7860090.304</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B1235" t="n">
-        <v>9348543.609999999</v>
+        <v>14555529.314</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B1236" t="n">
-        <v>9876625.647</v>
+        <v>9250585.187000001</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B1237" t="n">
-        <v>16658702.812</v>
+        <v>17316630.871</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>9471646.251</v>
+        <v>9643468.957</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>15559579.28</v>
+        <v>22762705.257</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>11176294.018</v>
+        <v>15903527.022</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>15649596.102</v>
+        <v>14080491.729</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B1242" t="n">
-        <v>22213431.033</v>
+        <v>9348543.609999999</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B1243" t="n">
-        <v>14548570.861</v>
+        <v>9876625.647</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>18413104.776</v>
+        <v>16658702.812</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2022-05-14</t>
         </is>
       </c>
       <c r="B1245" t="n">
-        <v>10785396.841</v>
+        <v>9471646.251</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>20506438.825</v>
+        <v>15559579.28</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>8310304.394</v>
+        <v>11176294.018</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>8698898.304</v>
+        <v>15649596.102</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>8799800.285</v>
+        <v>22213431.033</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>19218055.445</v>
+        <v>14548570.861</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>14601308.011</v>
+        <v>18413104.776</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>12724123.607</v>
+        <v>10785396.841</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>14880148.605</v>
+        <v>20506438.825</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="B1254" t="n">
-        <v>9252340.935000001</v>
+        <v>8310304.394</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>8671524.054</v>
+        <v>8698898.304</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>18218036.776</v>
+        <v>8799800.285</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B1257" t="n">
-        <v>18095870.058</v>
+        <v>19218055.445</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>19014663.42</v>
+        <v>14601308.011</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B1259" t="n">
-        <v>9408798.934</v>
+        <v>12724123.607</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>16670126.739</v>
+        <v>14880148.605</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>16265749.775</v>
+        <v>9252340.935000001</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>8297333.426</v>
+        <v>8671524.054</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>21748228.097</v>
+        <v>18218036.776</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B1264" t="n">
-        <v>15610517.939</v>
+        <v>18095870.058</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="B1265" t="n">
-        <v>18752011.913</v>
+        <v>19014663.42</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>10512254.974</v>
+        <v>9408798.934</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>18684510.463</v>
+        <v>16670126.739</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="B1268" t="n">
-        <v>10958641.073</v>
+        <v>16265749.775</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>11167233.165</v>
+        <v>8297333.426</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B1270" t="n">
-        <v>17239012.79</v>
+        <v>21748228.097</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>18688241.354</v>
+        <v>15610517.939</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>22373304.463</v>
+        <v>18752011.913</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>14396933.475</v>
+        <v>10512254.974</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>14765108.135</v>
+        <v>18684510.463</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>12989124.134</v>
+        <v>10958641.073</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>10407093</v>
+        <v>11167233.165</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>19753403.705</v>
+        <v>17239012.79</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>8949049.268999999</v>
+        <v>18688241.354</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>22380338.022</v>
+        <v>22373304.463</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>12847069.898</v>
+        <v>14396933.475</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>18949481.536</v>
+        <v>14765108.135</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>21888949.44</v>
+        <v>12989124.134</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>20580745.394</v>
+        <v>10407093</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>19403702.941</v>
+        <v>19753403.705</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>12025387.77</v>
+        <v>8949049.268999999</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="B1286" t="n">
-        <v>11517746.211</v>
+        <v>22380338.022</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B1287" t="n">
-        <v>18648006.799</v>
+        <v>12847069.898</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2024-12-29</t>
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>18754649.599</v>
+        <v>18949481.536</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>18605805.647</v>
+        <v>21888949.44</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>22464882.776</v>
+        <v>20580745.394</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>19098735.371</v>
+        <v>19403702.941</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B1292" t="n">
-        <v>11437944.275</v>
+        <v>12025387.77</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>15630701.474</v>
+        <v>11517746.211</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>11711443.8</v>
+        <v>18648006.799</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B1295" t="n">
-        <v>8620307.16</v>
+        <v>18754649.599</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B1296" t="n">
-        <v>18515818.574</v>
+        <v>18605805.647</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>12856671.682</v>
+        <v>22464882.776</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>18201448.889</v>
+        <v>19098735.371</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B1299" t="n">
-        <v>9519524.592</v>
+        <v>11437944.275</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>18421861.334</v>
+        <v>15630701.474</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>18398573.918</v>
+        <v>11711443.8</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>9308642.501</v>
+        <v>8620307.16</v>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>17331183.271</v>
+        <v>18515818.574</v>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>10333719.079</v>
+        <v>12856671.682</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>20059958.476</v>
+        <v>18201448.889</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>9481051.257999999</v>
+        <v>9519524.592</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>12972917.766</v>
+        <v>18421861.334</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>12827728.942</v>
+        <v>18398573.918</v>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>10843259.392</v>
+        <v>9308642.501</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B1310" t="n">
-        <v>16829264.336</v>
+        <v>17331183.271</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>19069569.049</v>
+        <v>10333719.079</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B1312" t="n">
-        <v>9532015.716</v>
+        <v>20059958.476</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="B1313" t="n">
-        <v>17480511.655</v>
+        <v>9481051.257999999</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>12893419.954</v>
+        <v>12972917.766</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B1315" t="n">
-        <v>18930025.11</v>
+        <v>12827728.942</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>13592327.934</v>
+        <v>10843259.392</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>16884075.838</v>
+        <v>16829264.336</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>8363509.02</v>
+        <v>19069569.049</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2022-08-06</t>
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>12458643.374</v>
+        <v>9532015.716</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>11641354.93</v>
+        <v>17480511.655</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>16833334.95</v>
+        <v>12893419.954</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="B1322" t="n">
-        <v>17359924.278</v>
+        <v>18930025.11</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B1323" t="n">
-        <v>10236215.389</v>
+        <v>13592327.934</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>8049967.714</v>
+        <v>16884075.838</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>18172193.247</v>
+        <v>8363509.02</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B1326" t="n">
-        <v>18249350.163</v>
+        <v>12458643.374</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B1327" t="n">
-        <v>19357870.444</v>
+        <v>11641354.93</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B1328" t="n">
-        <v>18829096.598</v>
+        <v>16833334.95</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="B1329" t="n">
-        <v>11410435.924</v>
+        <v>17359924.278</v>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="B1330" t="n">
-        <v>11511228.874</v>
+        <v>10236215.389</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="B1331" t="n">
-        <v>11873870.808</v>
+        <v>8049967.714</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B1332" t="n">
-        <v>16905626.816</v>
+        <v>18172193.247</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B1333" t="n">
-        <v>9506750.107999999</v>
+        <v>18249350.163</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B1334" t="n">
-        <v>10121188.898</v>
+        <v>19357870.444</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B1335" t="n">
-        <v>15731904.375</v>
+        <v>18829096.598</v>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="B1336" t="n">
-        <v>10026685.713</v>
+        <v>11410435.924</v>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="B1337" t="n">
-        <v>8170042.55</v>
+        <v>11511228.874</v>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="B1338" t="n">
-        <v>6358468.879</v>
+        <v>11873870.808</v>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B1339" t="n">
-        <v>16560800.359</v>
+        <v>16905626.816</v>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="B1340" t="n">
-        <v>18211536.318</v>
+        <v>9506750.107999999</v>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>11004721.176</v>
+        <v>10121188.898</v>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="B1342" t="n">
-        <v>11867652.532</v>
+        <v>15731904.375</v>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B1343" t="n">
-        <v>12210206.289</v>
+        <v>10026685.713</v>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B1344" t="n">
-        <v>14873483.781</v>
+        <v>8170042.55</v>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="B1345" t="n">
-        <v>8536718.226</v>
+        <v>6358468.879</v>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B1346" t="n">
-        <v>12171617.905</v>
+        <v>16560800.359</v>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B1347" t="n">
-        <v>13510242.654</v>
+        <v>18211536.318</v>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B1348" t="n">
-        <v>19772264.652</v>
+        <v>11004721.176</v>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="B1349" t="n">
-        <v>16050259.512</v>
+        <v>11867652.532</v>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>8307154.455</v>
+        <v>12210206.289</v>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>2022-11-23</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B1351" t="n">
-        <v>10451472.456</v>
+        <v>14873483.781</v>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>14362928.781</v>
+        <v>8536718.226</v>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B1353" t="n">
-        <v>13491078.904</v>
+        <v>12171617.905</v>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B1354" t="n">
-        <v>20112719.639</v>
+        <v>13510242.654</v>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>20351324.136</v>
+        <v>19772264.652</v>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B1356" t="n">
-        <v>23088144.912</v>
+        <v>16050259.512</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B1357" t="n">
-        <v>14103054.216</v>
+        <v>8307154.455</v>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>19939698.057</v>
+        <v>10451472.456</v>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B1359" t="n">
-        <v>18996084.867</v>
+        <v>14362928.781</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B1360" t="n">
-        <v>10152643.862</v>
+        <v>13491078.904</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B1361" t="n">
-        <v>9239501.051000001</v>
+        <v>20112719.639</v>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>10510937.957</v>
+        <v>20351324.136</v>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B1363" t="n">
-        <v>15716836.044</v>
+        <v>23088144.912</v>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>2022-12-22</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>10615483.231</v>
+        <v>14103054.216</v>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="B1365" t="n">
-        <v>15740885.312</v>
+        <v>19939698.057</v>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B1366" t="n">
-        <v>12796519.886</v>
+        <v>18996084.867</v>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>13639848.875</v>
+        <v>10152643.862</v>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B1368" t="n">
-        <v>15795124.861</v>
+        <v>9239501.051000001</v>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="B1369" t="n">
-        <v>22404450.46</v>
+        <v>10510937.957</v>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="B1370" t="n">
-        <v>10477853.005</v>
+        <v>15716836.044</v>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>2023-01-07</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="B1371" t="n">
-        <v>11376341.238</v>
+        <v>10615483.231</v>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B1372" t="n">
-        <v>14589767.49</v>
+        <v>15740885.312</v>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>13432763.242</v>
+        <v>12796519.886</v>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="B1374" t="n">
-        <v>9914365.379000001</v>
+        <v>13639848.875</v>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B1375" t="n">
-        <v>8871469.16</v>
+        <v>15795124.861</v>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B1376" t="n">
-        <v>8821044.728</v>
+        <v>22404450.46</v>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>11260943.27</v>
+        <v>10477853.005</v>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-01-07</t>
         </is>
       </c>
       <c r="B1378" t="n">
-        <v>14551069.327</v>
+        <v>11376341.238</v>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B1379" t="n">
-        <v>10360571.322</v>
+        <v>14589767.49</v>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B1380" t="n">
-        <v>8654142.73</v>
+        <v>13432763.242</v>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B1381" t="n">
-        <v>7804497.859</v>
+        <v>9914365.379000001</v>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B1382" t="n">
-        <v>9388382.575999999</v>
+        <v>8871469.16</v>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B1383" t="n">
-        <v>9877779.377</v>
+        <v>8821044.728</v>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="B1384" t="n">
-        <v>10504922.862</v>
+        <v>11260943.27</v>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B1385" t="n">
-        <v>8660675.096000001</v>
+        <v>14551069.327</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="B1386" t="n">
-        <v>18609730.033</v>
+        <v>10360571.322</v>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>7349744.434</v>
+        <v>8654142.73</v>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="B1388" t="n">
-        <v>15643923.15</v>
+        <v>7804497.859</v>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B1389" t="n">
-        <v>18799096.649</v>
+        <v>9388382.575999999</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B1390" t="n">
-        <v>10857484.275</v>
+        <v>9877779.377</v>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="B1391" t="n">
-        <v>11149234.035</v>
+        <v>10504922.862</v>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B1392" t="n">
-        <v>15621689.103</v>
+        <v>8660675.096000001</v>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B1393" t="n">
-        <v>8127301.046</v>
+        <v>18609730.033</v>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>14446234.788</v>
+        <v>7349744.434</v>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>18209088.114</v>
+        <v>15643923.15</v>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B1396" t="n">
-        <v>10805935.58</v>
+        <v>18799096.649</v>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B1397" t="n">
-        <v>22365594.535</v>
+        <v>10857484.275</v>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>8486747.433</v>
+        <v>11149234.035</v>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>14010038.153</v>
+        <v>15621689.103</v>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>12870879.477</v>
+        <v>8127301.046</v>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B1401" t="n">
-        <v>15346852.871</v>
+        <v>14446234.788</v>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B1402" t="n">
-        <v>9114476.312000001</v>
+        <v>18209088.114</v>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="B1403" t="n">
-        <v>10847808.277</v>
+        <v>10805935.58</v>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B1404" t="n">
-        <v>8877780.388</v>
+        <v>22365594.535</v>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>22259727.582</v>
+        <v>8486747.433</v>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>17968690.541</v>
+        <v>14010038.153</v>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B1407" t="n">
-        <v>8346328.634</v>
+        <v>12870879.477</v>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B1408" t="n">
-        <v>18882222.042</v>
+        <v>15346852.871</v>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>9386582.370999999</v>
+        <v>9114476.312000001</v>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="B1410" t="n">
-        <v>10773183.386</v>
+        <v>10847808.277</v>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>16585261.576</v>
+        <v>8877780.388</v>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B1412" t="n">
-        <v>16236706.926</v>
+        <v>22259727.582</v>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B1413" t="n">
-        <v>21808754.591</v>
+        <v>17968690.541</v>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="B1414" t="n">
-        <v>20554065.145</v>
+        <v>8346328.634</v>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="B1415" t="n">
-        <v>7902657.124</v>
+        <v>18882222.042</v>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B1416" t="n">
-        <v>14252744.065</v>
+        <v>9386582.370999999</v>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B1417" t="n">
-        <v>10658742.561</v>
+        <v>10773183.386</v>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="B1418" t="n">
-        <v>18727823.649</v>
+        <v>16585261.576</v>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="B1419" t="n">
-        <v>10503343.65</v>
+        <v>16236706.926</v>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B1420" t="n">
-        <v>10785349.848</v>
+        <v>21808754.591</v>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B1421" t="n">
-        <v>18803774.412</v>
+        <v>20554065.145</v>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="B1422" t="n">
-        <v>18746833.543</v>
+        <v>7902657.124</v>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B1423" t="n">
-        <v>14696488.122</v>
+        <v>14252744.065</v>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B1424" t="n">
-        <v>13074131.781</v>
+        <v>10658742.561</v>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B1425" t="n">
-        <v>11136369.663</v>
+        <v>18727823.649</v>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B1426" t="n">
-        <v>22620694.513</v>
+        <v>10503343.65</v>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>19760413.223</v>
+        <v>10785349.848</v>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B1428" t="n">
-        <v>11420107.846</v>
+        <v>18803774.412</v>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B1429" t="n">
-        <v>12841467.318</v>
+        <v>18746833.543</v>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B1430" t="n">
-        <v>19272529.034</v>
+        <v>14696488.122</v>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B1431" t="n">
-        <v>11384746.006</v>
+        <v>13074131.781</v>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="B1432" t="n">
-        <v>19496972.836</v>
+        <v>11136369.663</v>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>12225489.867</v>
+        <v>22620694.513</v>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B1434" t="n">
-        <v>11477197.525</v>
+        <v>19760413.223</v>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="B1435" t="n">
-        <v>11313913.816</v>
+        <v>11420107.846</v>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B1436" t="n">
-        <v>18346710.052</v>
+        <v>12841467.318</v>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B1437" t="n">
-        <v>18616838.388</v>
+        <v>19272529.034</v>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B1438" t="n">
-        <v>16688077.13</v>
+        <v>11384746.006</v>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B1439" t="n">
-        <v>19740398.471</v>
+        <v>19496972.836</v>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B1440" t="n">
-        <v>8386250.008</v>
+        <v>12225489.867</v>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="B1441" t="n">
-        <v>15303734.889</v>
+        <v>11477197.525</v>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>11978202.448</v>
+        <v>11313913.816</v>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B1443" t="n">
-        <v>16127948.086</v>
+        <v>18346710.052</v>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>19006487.04</v>
+        <v>18616838.388</v>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>17569350.656</v>
+        <v>16688077.13</v>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>17249482.25</v>
+        <v>19740398.471</v>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="B1447" t="n">
-        <v>17225229.436</v>
+        <v>8386250.008</v>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B1448" t="n">
-        <v>17153769.299</v>
+        <v>15303734.889</v>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>17115867.282</v>
+        <v>11978202.448</v>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>17049245.734</v>
+        <v>16127948.086</v>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>16833063.951</v>
+        <v>19006487.04</v>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>16784620.262</v>
+        <v>17569350.656</v>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>12895454.923</v>
+        <v>17249482.25</v>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B1454" t="n">
-        <v>11691372.317</v>
+        <v>17225229.436</v>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="B1455" t="n">
+        <v>17153769.299</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="B1456" t="n">
+        <v>17115867.282</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="B1457" t="n">
+        <v>17049245.734</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="B1458" t="n">
+        <v>16833063.951</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="B1459" t="n">
+        <v>16784620.262</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B1460" t="n">
+        <v>12895454.923</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="B1461" t="n">
+        <v>11691372.317</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="B1455" t="n">
+      <c r="B1462" t="n">
         <v>16110702.506</v>
       </c>
     </row>
